--- a/report/merged_configurations.xlsx
+++ b/report/merged_configurations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5353" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5320" uniqueCount="1292">
   <si>
     <t>title</t>
   </si>
@@ -3855,6 +3855,39 @@
   </si>
   <si>
     <t>https://data.vlaanderen.be/doc/concept/StandaardStatus/KandidaatStandaard</t>
+  </si>
+  <si>
+    <t>OSLO SSN SOSA VL</t>
+  </si>
+  <si>
+    <t>https://data.vlaanderen.be/id/concept/StandaardType/Interoperabiliteit</t>
+  </si>
+  <si>
+    <t>SSNSOSA-description.md</t>
+  </si>
+  <si>
+    <t>[{"name":"Datavoorbeelden SSN SOSA VL","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/tree/main/resources"}]</t>
+  </si>
+  <si>
+    <t>Charter SSNSOSAVL</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/charter/Template-Werkgroep-Charter-OSLO.docx</t>
+  </si>
+  <si>
+    <t>[{"name":"Verslag Business Werkgroep - 3 december 2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/reports/Verslag%20-%20Business%20werkgroep%20SSN%20SOSA%20VL.pdf"},{"name":"Verslag Thematische Werkgroep 1 - 14 januari 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/reports/Verslag%20Thematische%20werkgroep%201%20-%20SSN%20SOSA%20%202026-02-02.pdf"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Presentatie Business Werkgroep -  3 december 2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/presentations/SSN%20SOSA%20VL%20Business%20Werkgroep.pdf"},{"name":"Presentatie Thematische Werkgroep 1 - 14 januari 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/presentations/Presentatie%20SSN%20SOSA%20VL%20Thematische%20werkgroep%201.pdf"}]</t>
+  </si>
+  <si>
+    <t>https://data.vlaanderen.be/doc/concept/Domein/Omgeving</t>
+  </si>
+  <si>
+    <t>Inspiratiebundel met betrekking tot SSN SOSA VL</t>
+  </si>
+  <si>
+    <t>{"name":"Charter SSNSOSAVL","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/charter/Template-Werkgroep-Charter-OSLO.docx"}</t>
   </si>
 </sst>
 </file>
@@ -4262,7 +4295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y258"/>
+  <dimension ref="A1:Y257"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="25" width="44" customWidth="1"/>
@@ -23074,155 +23107,68 @@
     </row>
     <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>37</v>
+        <v>1281</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>37</v>
+        <v>1282</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>37</v>
+        <v>767</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
+      </c>
+      <c r="F257" s="4">
+        <v>46072</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>37</v>
+        <v>1283</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I257" s="3" t="s">
-        <v>37</v>
+        <v>1284</v>
       </c>
       <c r="J257" s="3" t="s">
-        <v>37</v>
+        <v>1285</v>
       </c>
       <c r="K257" s="3" t="s">
-        <v>37</v>
+        <v>1286</v>
       </c>
       <c r="L257" s="3" t="s">
-        <v>37</v>
+        <v>1287</v>
       </c>
       <c r="M257" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N257" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O257" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P257" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q257" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R257" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="S257" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>1288</v>
+      </c>
+      <c r="N257" s="4">
+        <v>45974</v>
+      </c>
+      <c r="O257" s="3"/>
+      <c r="P257" s="3"/>
+      <c r="Q257" s="3"/>
+      <c r="R257" s="3"/>
+      <c r="S257" s="3"/>
       <c r="T257" s="3" t="s">
-        <v>37</v>
+        <v>1289</v>
       </c>
       <c r="U257" s="3" t="s">
         <v>37</v>
       </c>
       <c r="V257" s="3" t="s">
-        <v>37</v>
+        <v>1290</v>
       </c>
       <c r="W257" s="3" t="s">
         <v>37</v>
       </c>
       <c r="X257" s="3" t="s">
-        <v>37</v>
+        <v>1291</v>
       </c>
       <c r="Y257" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="S258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="T258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="U258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="W258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="X258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y258" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -23234,7 +23180,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R258"/>
+  <dimension ref="A1:R257"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="18" width="44" customWidth="1"/>
@@ -37578,37 +37524,37 @@
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="B257" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="C257" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D257" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E257" s="6" t="b">
-        <v>0</v>
+        <v>1281</v>
+      </c>
+      <c r="B257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E257" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="F257" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G257" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H257" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I257" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J257" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K257" s="6" t="b">
-        <v>0</v>
+      <c r="G257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K257" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="L257" s="6" t="b">
         <v>0</v>
@@ -37625,67 +37571,11 @@
       <c r="P257" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="Q257" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R257" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A258" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="B258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="C258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R258" s="6" t="b">
-        <v>0</v>
+      <c r="Q257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R257" s="5" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/report/merged_configurations.xlsx
+++ b/report/merged_configurations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5320" uniqueCount="1292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5308" uniqueCount="1291">
   <si>
     <t>title</t>
   </si>
@@ -3852,9 +3852,6 @@
   </si>
   <si>
     <t>Vocabularium Rooilijnplannen</t>
-  </si>
-  <si>
-    <t>https://data.vlaanderen.be/doc/concept/StandaardStatus/KandidaatStandaard</t>
   </si>
   <si>
     <t>OSLO SSN SOSA VL</t>
@@ -15815,7 +15812,7 @@
         <v>27</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>151</v>
@@ -15850,8 +15847,8 @@
       <c r="O158" s="4">
         <v>46030</v>
       </c>
-      <c r="P158" s="3" t="s">
-        <v>121</v>
+      <c r="P158" s="4">
+        <v>46073</v>
       </c>
       <c r="Q158" s="3"/>
       <c r="R158" s="3" t="s">
@@ -15888,7 +15885,7 @@
         <v>27</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>151</v>
@@ -15923,8 +15920,8 @@
       <c r="O159" s="4">
         <v>46030</v>
       </c>
-      <c r="P159" s="3" t="s">
-        <v>121</v>
+      <c r="P159" s="4">
+        <v>46073</v>
       </c>
       <c r="Q159" s="3"/>
       <c r="R159" s="3" t="s">
@@ -15961,7 +15958,7 @@
         <v>27</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>151</v>
@@ -15996,8 +15993,8 @@
       <c r="O160" s="4">
         <v>46030</v>
       </c>
-      <c r="P160" s="3" t="s">
-        <v>121</v>
+      <c r="P160" s="4">
+        <v>46073</v>
       </c>
       <c r="Q160" s="3"/>
       <c r="R160" s="3" t="s">
@@ -19396,7 +19393,7 @@
         <v>27</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>29</v>
@@ -19428,11 +19425,11 @@
       <c r="N207" s="4">
         <v>45974</v>
       </c>
-      <c r="O207" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="P207" s="3" t="s">
-        <v>121</v>
+      <c r="O207" s="4">
+        <v>46030</v>
+      </c>
+      <c r="P207" s="4">
+        <v>46073</v>
       </c>
       <c r="Q207" s="3"/>
       <c r="R207" s="4">
@@ -22810,7 +22807,7 @@
         <v>27</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>29</v>
@@ -22842,11 +22839,11 @@
       <c r="N253" s="4">
         <v>45743</v>
       </c>
-      <c r="O253" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="P253" s="3" t="s">
-        <v>121</v>
+      <c r="O253" s="4">
+        <v>46030</v>
+      </c>
+      <c r="P253" s="4">
+        <v>46065</v>
       </c>
       <c r="Q253" s="4">
         <v>45867</v>
@@ -22854,8 +22851,8 @@
       <c r="R253" s="4">
         <v>45961</v>
       </c>
-      <c r="S253" s="3" t="s">
-        <v>121</v>
+      <c r="S253" s="3">
+        <v>0</v>
       </c>
       <c r="T253" s="3" t="s">
         <v>109</v>
@@ -22887,7 +22884,7 @@
         <v>27</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>29</v>
@@ -22919,11 +22916,11 @@
       <c r="N254" s="4">
         <v>45666</v>
       </c>
-      <c r="O254" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="P254" s="3" t="s">
-        <v>121</v>
+      <c r="O254" s="4">
+        <v>46030</v>
+      </c>
+      <c r="P254" s="4">
+        <v>46065</v>
       </c>
       <c r="Q254" s="4">
         <v>45858</v>
@@ -22964,7 +22961,7 @@
         <v>27</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>1280</v>
+        <v>63</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>29</v>
@@ -22996,11 +22993,11 @@
       <c r="N255" s="4">
         <v>45666</v>
       </c>
-      <c r="O255" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="P255" s="3" t="s">
-        <v>121</v>
+      <c r="O255" s="4">
+        <v>46030</v>
+      </c>
+      <c r="P255" s="4">
+        <v>46065</v>
       </c>
       <c r="Q255" s="4">
         <v>45858</v>
@@ -23107,10 +23104,10 @@
     </row>
     <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B257" s="3" t="s">
         <v>1281</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>1282</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>27</v>
@@ -23125,25 +23122,25 @@
         <v>46072</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I257" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J257" s="3" t="s">
         <v>1284</v>
       </c>
-      <c r="J257" s="3" t="s">
+      <c r="K257" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="K257" s="3" t="s">
+      <c r="L257" s="3" t="s">
         <v>1286</v>
       </c>
-      <c r="L257" s="3" t="s">
+      <c r="M257" s="3" t="s">
         <v>1287</v>
-      </c>
-      <c r="M257" s="3" t="s">
-        <v>1288</v>
       </c>
       <c r="N257" s="4">
         <v>45974</v>
@@ -23154,19 +23151,19 @@
       <c r="R257" s="3"/>
       <c r="S257" s="3"/>
       <c r="T257" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="U257" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V257" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="U257" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V257" s="3" t="s">
+      <c r="W257" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="X257" s="3" t="s">
         <v>1290</v>
-      </c>
-      <c r="W257" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="X257" s="3" t="s">
-        <v>1291</v>
       </c>
       <c r="Y257" s="3" t="s">
         <v>37</v>
@@ -32015,8 +32012,8 @@
       <c r="L158" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="M158" s="6" t="b">
-        <v>0</v>
+      <c r="M158" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N158" s="6" t="b">
         <v>0</v>
@@ -32071,8 +32068,8 @@
       <c r="L159" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="M159" s="6" t="b">
-        <v>0</v>
+      <c r="M159" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N159" s="6" t="b">
         <v>0</v>
@@ -32127,8 +32124,8 @@
       <c r="L160" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="M160" s="6" t="b">
-        <v>0</v>
+      <c r="M160" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N160" s="6" t="b">
         <v>0</v>
@@ -34756,11 +34753,11 @@
       <c r="K207" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L207" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M207" s="6" t="b">
-        <v>0</v>
+      <c r="L207" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M207" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N207" s="6" t="b">
         <v>0</v>
@@ -37332,11 +37329,11 @@
       <c r="K253" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L253" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M253" s="6" t="b">
-        <v>0</v>
+      <c r="L253" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M253" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N253" s="5" t="b">
         <v>1</v>
@@ -37344,8 +37341,8 @@
       <c r="O253" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="P253" s="6" t="b">
-        <v>0</v>
+      <c r="P253" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="Q253" s="5" t="b">
         <v>1</v>
@@ -37388,11 +37385,11 @@
       <c r="K254" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L254" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M254" s="6" t="b">
-        <v>0</v>
+      <c r="L254" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M254" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N254" s="5" t="b">
         <v>1</v>
@@ -37444,11 +37441,11 @@
       <c r="K255" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L255" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M255" s="6" t="b">
-        <v>0</v>
+      <c r="L255" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M255" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N255" s="5" t="b">
         <v>1</v>
@@ -37524,7 +37521,7 @@
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B257" s="5" t="b">
         <v>1</v>

--- a/report/merged_configurations.xlsx
+++ b/report/merged_configurations.xlsx
@@ -134,13 +134,16 @@
     <t>Applicatieprofiel Thermografische Gebouwanalyse</t>
   </si>
   <si>
+    <t>https://data.vlaanderen.be/id/concept/StandaardStatus/ErkendeStandaard</t>
+  </si>
+  <si>
     <t>thermai-description.md</t>
   </si>
   <si>
     <t>[{"name":"Applicatieprofiel Thermografische Gebouwanalyse","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/thermografische-gebouwanalyse"}]</t>
   </si>
   <si>
-    <t>[{"name":"Modelleerrapport","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-thermAI/blob/main/resources/ModelleerrapportThermAI.pdf"},{"name":"Datavoorbeelden","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-thermAI/tree/main/resources/Datavoorbeelden"}]</t>
+    <t>[{"name":"Modelleerrapport","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/main/resources/ModelleerrapportThermAI.pdf"},{"name":"Datavoorbeelden","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-thermAI/tree/main/resources/Datavoorbeelden"}]</t>
   </si>
   <si>
     <t>Charter Thermografische Gebouwanalyse</t>
@@ -149,10 +152,10 @@
     <t>https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/charter/Charter_OSLO_thermAI.pdf</t>
   </si>
   <si>
-    <t>[{"name":"Verslag Business werkgroep - 18-02-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/reports/Business%20werkgroep%20CoT%20ThermAI%202025-02-18.pdf"},{"name":"Verslag Thematische Werkgroep 1 - 18-03-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/reports/Thematische%20werkgroep%201%20-%20CoT%20ThermAI%202025-03-18.pdf"},{"name":"Verslag Thematische Werkgroep 2 - 15-04-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/reports/Thematische%20werkgroep%202%20-%20CoT%20ThermAI%202025-04-15.pdf"},{"name":"Verslag Thematische Werkgroep 3 - 15-05-2025","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-thermAI/blob/standaardenregister/reports/Verslag%20Thematische%20werkgroep%203%20-%20CoT%20ThermAI%202025-04-15.docx.pdf"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Presentatie Business Werkgroep - 18-02-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/presentations/ThermAI%20Business%20Werkgroep%20(1).pdf"},{"name":"Presentatie Thematische Werkgroep 1 - 18-03-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/presentations/Thematische%20werkgroep%201%20-%20ThermAI.pdf"},{"name":"Presentatie Thematische Werkgroep 2 - 15-04-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/presentations/Thematische%20werkgroep%202%20-%20ThermAI.pdf"},{"name":"Presentatie Thematische Werkgroep 3 - 15-05-2025","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-thermAI/blob/standaardenregister/presentations/Slides%20-%20Thematische%20werkgroep%203%20-%20ThermAI.pdf"}]</t>
+    <t>[{"name":"Verslag Business werkgroep - 18-02-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/reports/Business%20werkgroep%20CoT%20ThermAI%202025-02-18.pdf"},{"name":"Verslag Thematische Werkgroep 1 - 18-03-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/reports/Thematische%20werkgroep%201%20-%20CoT%20ThermAI%202025-03-18.pdf"},{"name":"Verslag Thematische Werkgroep 2 - 15-04-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/reports/Thematische%20werkgroep%202%20-%20CoT%20ThermAI%202025-04-15.pdf"},{"name":"Verslag Thematische Werkgroep 3 - 15-05-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/reports/Verslag%20Thematische%20werkgroep%203%20-%20CoT%20ThermAI%202025-04-15.docx.pdf"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Presentatie Business Werkgroep - 18-02-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/presentations/ThermAI%20Business%20Werkgroep%20(1).pdf"},{"name":"Presentatie Thematische Werkgroep 1 - 18-03-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/presentations/Thematische%20werkgroep%201%20-%20ThermAI.pdf"},{"name":"Presentatie Thematische Werkgroep 2 - 15-04-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/presentations/Thematische%20werkgroep%202%20-%20ThermAI.pdf"},{"name":"Presentatie Thematische Werkgroep 3 - 15-05-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-thermAI/standaardenregister/presentations/Slides%20-%20Thematische%20werkgroep%203%20-%20ThermAI.pdf"}]</t>
   </si>
   <si>
     <t>2024-12-1</t>
@@ -201,9 +204,6 @@
   </si>
   <si>
     <t>Applicatieprofiel Energiehuis</t>
-  </si>
-  <si>
-    <t>https://data.vlaanderen.be/id/concept/StandaardStatus/ErkendeStandaard</t>
   </si>
   <si>
     <t>energiehuis-description.md</t>
@@ -4460,40 +4460,42 @@
         <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F3" s="4">
-        <v>45799</v>
+        <v>46002</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
+      <c r="P3" s="4">
+        <v>46002</v>
+      </c>
       <c r="Q3" s="4">
         <v>45854</v>
       </c>
@@ -4502,7 +4504,7 @@
       </c>
       <c r="S3" s="3"/>
       <c r="T3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U3" s="3" t="s">
         <v>37</v>
@@ -4514,7 +4516,7 @@
         <v>37</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>37</v>
@@ -4522,7 +4524,7 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>26</v>
@@ -4534,31 +4536,31 @@
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F4" s="4">
         <v>45889</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N4" s="4">
         <v>45428</v>
@@ -4573,19 +4575,19 @@
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W4" s="3" t="s">
         <v>37</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>37</v>
@@ -4593,7 +4595,7 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>26</v>
@@ -4602,7 +4604,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>29</v>
@@ -4677,7 +4679,7 @@
         <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>29</v>
@@ -4752,7 +4754,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>80</v>
@@ -4827,7 +4829,7 @@
         <v>27</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>80</v>
@@ -4902,7 +4904,7 @@
         <v>27</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>29</v>
@@ -4973,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>29</v>
@@ -5044,7 +5046,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>29</v>
@@ -5113,7 +5115,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>29</v>
@@ -5182,7 +5184,7 @@
         <v>27</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>115</v>
@@ -5255,7 +5257,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>115</v>
@@ -5328,7 +5330,7 @@
         <v>27</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>29</v>
@@ -5403,7 +5405,7 @@
         <v>27</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>29</v>
@@ -5478,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>29</v>
@@ -5768,7 +5770,7 @@
         <v>27</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>29</v>
@@ -5843,7 +5845,7 @@
         <v>27</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>29</v>
@@ -5991,7 +5993,7 @@
         <v>27</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>29</v>
@@ -6068,7 +6070,7 @@
         <v>27</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>29</v>
@@ -6145,7 +6147,7 @@
         <v>27</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>29</v>
@@ -6218,7 +6220,7 @@
         <v>27</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>29</v>
@@ -6291,7 +6293,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>216</v>
@@ -6364,7 +6366,7 @@
         <v>27</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>216</v>
@@ -7329,7 +7331,7 @@
         <v>27</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>230</v>
@@ -7404,7 +7406,7 @@
         <v>27</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>230</v>
@@ -7625,7 +7627,7 @@
         <v>27</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>230</v>
@@ -7700,7 +7702,7 @@
         <v>27</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>230</v>
@@ -7775,7 +7777,7 @@
         <v>27</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>230</v>
@@ -7850,7 +7852,7 @@
         <v>27</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>230</v>
@@ -7925,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>308</v>
@@ -7998,7 +8000,7 @@
         <v>27</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>308</v>
@@ -8363,7 +8365,7 @@
         <v>27</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>349</v>
@@ -8436,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>349</v>
@@ -8509,7 +8511,7 @@
         <v>27</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>349</v>
@@ -8582,7 +8584,7 @@
         <v>27</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>349</v>
@@ -8655,7 +8657,7 @@
         <v>27</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>29</v>
@@ -8801,7 +8803,7 @@
         <v>27</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>29</v>
@@ -8947,7 +8949,7 @@
         <v>27</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>29</v>
@@ -9020,7 +9022,7 @@
         <v>27</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>29</v>
@@ -9093,7 +9095,7 @@
         <v>27</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>29</v>
@@ -9239,7 +9241,7 @@
         <v>27</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>414</v>
@@ -9312,7 +9314,7 @@
         <v>27</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
@@ -9608,7 +9610,7 @@
         <v>27</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>448</v>
@@ -9681,7 +9683,7 @@
         <v>27</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>448</v>
@@ -9827,7 +9829,7 @@
         <v>27</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>29</v>
@@ -10119,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>29</v>
@@ -10192,7 +10194,7 @@
         <v>27</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
@@ -10265,7 +10267,7 @@
         <v>27</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>29</v>
@@ -10338,7 +10340,7 @@
         <v>27</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
@@ -10411,7 +10413,7 @@
         <v>27</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>29</v>
@@ -10484,7 +10486,7 @@
         <v>27</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>513</v>
@@ -10557,7 +10559,7 @@
         <v>27</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>513</v>
@@ -10776,7 +10778,7 @@
         <v>27</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>540</v>
@@ -10849,7 +10851,7 @@
         <v>27</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>540</v>
@@ -10922,7 +10924,7 @@
         <v>27</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>540</v>
@@ -10995,7 +10997,7 @@
         <v>27</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>540</v>
@@ -11112,7 +11114,7 @@
       </c>
       <c r="S93" s="3"/>
       <c r="T93" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U93" s="3" t="s">
         <v>37</v>
@@ -11141,7 +11143,7 @@
         <v>27</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>29</v>
@@ -11185,7 +11187,7 @@
       </c>
       <c r="S94" s="3"/>
       <c r="T94" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>37</v>
@@ -11214,7 +11216,7 @@
         <v>27</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>29</v>
@@ -11287,7 +11289,7 @@
         <v>27</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>29</v>
@@ -11360,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>595</v>
@@ -11433,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>595</v>
@@ -11506,7 +11508,7 @@
         <v>27</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>595</v>
@@ -11579,7 +11581,7 @@
         <v>27</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>595</v>
@@ -11652,7 +11654,7 @@
         <v>27</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>616</v>
@@ -11725,7 +11727,7 @@
         <v>625</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>616</v>
@@ -11798,7 +11800,7 @@
         <v>27</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>616</v>
@@ -11871,7 +11873,7 @@
         <v>625</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>616</v>
@@ -11944,7 +11946,7 @@
         <v>625</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>616</v>
@@ -12017,7 +12019,7 @@
         <v>643</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>29</v>
@@ -12061,7 +12063,7 @@
       </c>
       <c r="S106" s="3"/>
       <c r="T106" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U106" s="3" t="s">
         <v>37</v>
@@ -12090,7 +12092,7 @@
         <v>643</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>29</v>
@@ -12134,7 +12136,7 @@
       </c>
       <c r="S107" s="3"/>
       <c r="T107" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U107" s="3" t="s">
         <v>37</v>
@@ -12163,7 +12165,7 @@
         <v>27</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>29</v>
@@ -12207,7 +12209,7 @@
       </c>
       <c r="S108" s="3"/>
       <c r="T108" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U108" s="3" t="s">
         <v>37</v>
@@ -12236,7 +12238,7 @@
         <v>27</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>29</v>
@@ -12309,7 +12311,7 @@
         <v>27</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>29</v>
@@ -12382,7 +12384,7 @@
         <v>27</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>29</v>
@@ -12455,7 +12457,7 @@
         <v>27</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>29</v>
@@ -12528,7 +12530,7 @@
         <v>27</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>29</v>
@@ -12601,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>29</v>
@@ -12674,7 +12676,7 @@
         <v>27</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>29</v>
@@ -12747,7 +12749,7 @@
         <v>27</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>29</v>
@@ -12820,7 +12822,7 @@
         <v>27</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>29</v>
@@ -12893,7 +12895,7 @@
         <v>27</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>29</v>
@@ -12966,7 +12968,7 @@
         <v>27</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>29</v>
@@ -13039,7 +13041,7 @@
         <v>27</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>29</v>
@@ -13112,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>29</v>
@@ -13185,7 +13187,7 @@
         <v>27</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>29</v>
@@ -13258,7 +13260,7 @@
         <v>27</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>29</v>
@@ -13331,7 +13333,7 @@
         <v>27</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>29</v>
@@ -13477,7 +13479,7 @@
         <v>27</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>414</v>
@@ -13550,7 +13552,7 @@
         <v>27</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>414</v>
@@ -13623,7 +13625,7 @@
         <v>27</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>308</v>
@@ -13696,7 +13698,7 @@
         <v>27</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>308</v>
@@ -13769,7 +13771,7 @@
         <v>27</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>308</v>
@@ -14205,7 +14207,7 @@
         <v>27</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>29</v>
@@ -14278,7 +14280,7 @@
         <v>27</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>29</v>
@@ -14351,7 +14353,7 @@
         <v>27</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>29</v>
@@ -14424,7 +14426,7 @@
         <v>27</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>29</v>
@@ -14497,7 +14499,7 @@
         <v>27</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>29</v>
@@ -14570,7 +14572,7 @@
         <v>27</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>29</v>
@@ -14643,7 +14645,7 @@
         <v>27</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>29</v>
@@ -14716,7 +14718,7 @@
         <v>27</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>29</v>
@@ -14789,7 +14791,7 @@
         <v>27</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>29</v>
@@ -14862,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>29</v>
@@ -14935,7 +14937,7 @@
         <v>27</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>29</v>
@@ -15008,7 +15010,7 @@
         <v>27</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>29</v>
@@ -15081,7 +15083,7 @@
         <v>27</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>29</v>
@@ -15154,7 +15156,7 @@
         <v>27</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>29</v>
@@ -15227,7 +15229,7 @@
         <v>27</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>29</v>
@@ -15300,7 +15302,7 @@
         <v>27</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>29</v>
@@ -15373,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>29</v>
@@ -15446,7 +15448,7 @@
         <v>27</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>29</v>
@@ -15519,7 +15521,7 @@
         <v>27</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>29</v>
@@ -15592,7 +15594,7 @@
         <v>27</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>29</v>
@@ -15665,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>29</v>
@@ -15815,7 +15817,7 @@
         <v>27</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>151</v>
@@ -15859,7 +15861,7 @@
       </c>
       <c r="S158" s="3"/>
       <c r="T158" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U158" s="3" t="s">
         <v>37</v>
@@ -15888,7 +15890,7 @@
         <v>27</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>151</v>
@@ -15932,7 +15934,7 @@
       </c>
       <c r="S159" s="3"/>
       <c r="T159" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U159" s="3" t="s">
         <v>37</v>
@@ -15961,7 +15963,7 @@
         <v>27</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>151</v>
@@ -16034,7 +16036,7 @@
         <v>27</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>704</v>
@@ -16107,7 +16109,7 @@
         <v>27</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>704</v>
@@ -16180,7 +16182,7 @@
         <v>27</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>704</v>
@@ -16253,7 +16255,7 @@
         <v>27</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>704</v>
@@ -16326,7 +16328,7 @@
         <v>27</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>704</v>
@@ -16399,7 +16401,7 @@
         <v>27</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>704</v>
@@ -16472,7 +16474,7 @@
         <v>27</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>704</v>
@@ -16545,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>704</v>
@@ -16618,7 +16620,7 @@
         <v>27</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>704</v>
@@ -16691,7 +16693,7 @@
         <v>27</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>704</v>
@@ -16764,7 +16766,7 @@
         <v>27</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>704</v>
@@ -16837,7 +16839,7 @@
         <v>27</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>704</v>
@@ -16910,7 +16912,7 @@
         <v>27</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>704</v>
@@ -16983,7 +16985,7 @@
         <v>27</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>704</v>
@@ -17056,7 +17058,7 @@
         <v>27</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>704</v>
@@ -17129,7 +17131,7 @@
         <v>27</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>704</v>
@@ -17202,7 +17204,7 @@
         <v>27</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>704</v>
@@ -17275,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>704</v>
@@ -17348,7 +17350,7 @@
         <v>27</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>704</v>
@@ -17421,7 +17423,7 @@
         <v>27</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>704</v>
@@ -17494,7 +17496,7 @@
         <v>27</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>704</v>
@@ -17567,7 +17569,7 @@
         <v>27</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>704</v>
@@ -17640,7 +17642,7 @@
         <v>27</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>704</v>
@@ -17713,7 +17715,7 @@
         <v>27</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>704</v>
@@ -17786,7 +17788,7 @@
         <v>27</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>704</v>
@@ -17859,7 +17861,7 @@
         <v>27</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>704</v>
@@ -17932,7 +17934,7 @@
         <v>27</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>704</v>
@@ -18005,7 +18007,7 @@
         <v>27</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>704</v>
@@ -18078,7 +18080,7 @@
         <v>27</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>704</v>
@@ -18151,7 +18153,7 @@
         <v>27</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>704</v>
@@ -18224,7 +18226,7 @@
         <v>27</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>704</v>
@@ -18297,7 +18299,7 @@
         <v>27</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>704</v>
@@ -18370,7 +18372,7 @@
         <v>27</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>704</v>
@@ -18443,7 +18445,7 @@
         <v>27</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>704</v>
@@ -18516,7 +18518,7 @@
         <v>27</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>704</v>
@@ -18589,7 +18591,7 @@
         <v>27</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>704</v>
@@ -18662,7 +18664,7 @@
         <v>27</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>704</v>
@@ -18735,7 +18737,7 @@
         <v>27</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>704</v>
@@ -18808,7 +18810,7 @@
         <v>27</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>704</v>
@@ -18881,7 +18883,7 @@
         <v>27</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>704</v>
@@ -18954,7 +18956,7 @@
         <v>27</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>704</v>
@@ -18998,7 +19000,7 @@
       </c>
       <c r="S201" s="3"/>
       <c r="T201" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U201" s="3" t="s">
         <v>37</v>
@@ -19250,7 +19252,7 @@
         <v>27</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>29</v>
@@ -19294,7 +19296,7 @@
       </c>
       <c r="S205" s="3"/>
       <c r="T205" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U205" s="3" t="s">
         <v>37</v>
@@ -19396,7 +19398,7 @@
         <v>27</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>29</v>
@@ -19440,7 +19442,7 @@
       </c>
       <c r="S207" s="3"/>
       <c r="T207" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U207" s="3" t="s">
         <v>37</v>
@@ -19469,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>29</v>
@@ -19542,7 +19544,7 @@
         <v>27</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>29</v>
@@ -19615,7 +19617,7 @@
         <v>27</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>29</v>
@@ -19659,7 +19661,7 @@
       </c>
       <c r="S210" s="3"/>
       <c r="T210" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U210" s="3" t="s">
         <v>37</v>
@@ -19688,7 +19690,7 @@
         <v>27</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>29</v>
@@ -20061,7 +20063,7 @@
         <v>27</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>29</v>
@@ -20132,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>29</v>
@@ -20251,7 +20253,7 @@
         <v>121</v>
       </c>
       <c r="T218" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U218" s="3" t="s">
         <v>37</v>
@@ -20328,7 +20330,7 @@
         <v>121</v>
       </c>
       <c r="T219" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U219" s="3" t="s">
         <v>37</v>
@@ -20357,7 +20359,7 @@
         <v>27</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>29</v>
@@ -20430,7 +20432,7 @@
         <v>27</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>29</v>
@@ -20801,7 +20803,7 @@
         <v>27</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>29</v>
@@ -20876,7 +20878,7 @@
         <v>27</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>29</v>
@@ -20951,7 +20953,7 @@
         <v>27</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>1120</v>
@@ -21024,7 +21026,7 @@
         <v>27</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>1120</v>
@@ -21097,7 +21099,7 @@
         <v>27</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>616</v>
@@ -21170,7 +21172,7 @@
         <v>27</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>616</v>
@@ -21243,7 +21245,7 @@
         <v>27</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>29</v>
@@ -21320,7 +21322,7 @@
         <v>27</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>29</v>
@@ -21397,7 +21399,7 @@
         <v>27</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>1071</v>
@@ -21470,7 +21472,7 @@
         <v>27</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>1071</v>
@@ -21543,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>1071</v>
@@ -21616,7 +21618,7 @@
         <v>27</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>29</v>
@@ -21985,7 +21987,7 @@
         <v>27</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>1071</v>
@@ -22033,7 +22035,7 @@
         <v>121</v>
       </c>
       <c r="T242" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U242" s="3" t="s">
         <v>37</v>
@@ -22281,7 +22283,7 @@
         <v>27</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>29</v>
@@ -22358,7 +22360,7 @@
         <v>27</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>29</v>
@@ -22581,7 +22583,7 @@
         <v>27</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>29</v>
@@ -22658,7 +22660,7 @@
         <v>27</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>29</v>
@@ -22735,7 +22737,7 @@
         <v>27</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>29</v>
@@ -22810,7 +22812,7 @@
         <v>27</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>29</v>
@@ -22887,7 +22889,7 @@
         <v>27</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>1269</v>
@@ -22964,7 +22966,7 @@
         <v>27</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>1269</v>
@@ -23335,8 +23337,8 @@
       <c r="L3" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M3" s="6" t="b">
-        <v>0</v>
+      <c r="M3" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N3" s="5" t="b">
         <v>1</v>
@@ -23356,7 +23358,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="5" t="b">
         <v>1</v>
@@ -23412,7 +23414,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="5" t="b">
         <v>1</v>

--- a/report/merged_configurations.xlsx
+++ b/report/merged_configurations.xlsx
@@ -3899,7 +3899,7 @@
     <t>NDNN-description.md</t>
   </si>
   <si>
-    <t>[{"name":"Implementatiemodel Nudging Down Night Noise","resourceReference":"https://data.vlaanderen.be/doc/implementatiemodel/nudgingdownnightnoise/"}]</t>
+    <t>[{"name":"Implementatiemodel Nudging Down Night Noise","resourceReference":"https://data.vlaanderen.be/doc/implementatiemodel/nudgingdownnightnoise/2026-04-14"}]</t>
   </si>
   <si>
     <t>Charter NDNN</t>
@@ -24763,7 +24763,7 @@
         <v>31</v>
       </c>
       <c r="F258" s="4">
-        <v>46129</v>
+        <v>46126</v>
       </c>
       <c r="G258" s="3" t="s">
         <v>1294</v>

--- a/report/merged_configurations.xlsx
+++ b/report/merged_configurations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5843" uniqueCount="1302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5843" uniqueCount="1301">
   <si>
     <t>title</t>
   </si>
@@ -3899,7 +3899,7 @@
     <t>NDNN-description.md</t>
   </si>
   <si>
-    <t>[{"name":"Implementatiemodel Nudging Down Night Noise","resourceReference":"https://data.vlaanderen.be/doc/implementatiemodel/nudgingdownnightnoise/2026-04-14"}]</t>
+    <t>[{"name":"Implementatiemodel Nudging Down Night Noise","resourceReference":"https://data.vlaanderen.be/doc/implementatiemodel/geluidsmeldingen-en-geluidsmetingen/ontwerpstandaard/2026-05-20"}]</t>
   </si>
   <si>
     <t>Charter NDNN</t>
@@ -3912,9 +3912,6 @@
   </si>
   <si>
     <t>[{"name":"Presentatie Business Werkgroep -  5 maart 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/presentations/Presentatie%20Business%20Werkgroep%20NDNN%2005-03-2026.pdf"},{"name":"Presentatie Thematische Werkgroep - 2 April 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/presentations/Presentatie%20Thematische%20werkgroep%201%20NDNN%2002-04-2026.pdf"}]</t>
-  </si>
-  <si>
-    <t>https://data.vlaanderen.be/id/concept/Domein/Werk</t>
   </si>
   <si>
     <t>{"name":"Charter NDNN","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/charter/Werkgroep%20charter%20OSLO_NudgingDownNightNoise.pdf"}</t>
@@ -8257,7 +8254,7 @@
         <v>310</v>
       </c>
       <c r="F50" s="4">
-        <v>44679</v>
+        <v>45546</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>311</v>
@@ -8324,7 +8321,7 @@
         <v>322</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>29</v>
@@ -8336,7 +8333,7 @@
         <v>310</v>
       </c>
       <c r="F51" s="4">
-        <v>44679</v>
+        <v>45546</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>323</v>
@@ -24795,7 +24792,7 @@
       <c r="R258" s="3"/>
       <c r="S258" s="3"/>
       <c r="T258" s="3" t="s">
-        <v>1300</v>
+        <v>90</v>
       </c>
       <c r="U258" s="3" t="s">
         <v>34</v>
@@ -24807,7 +24804,7 @@
         <v>39</v>
       </c>
       <c r="X258" s="3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="Y258" s="3" t="s">
         <v>39</v>

--- a/report/merged_configurations.xlsx
+++ b/report/merged_configurations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5843" uniqueCount="1301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5843" uniqueCount="1303">
   <si>
     <t>title</t>
   </si>
@@ -3863,7 +3863,7 @@
     <t>Vocabularium Rooilijnplannen</t>
   </si>
   <si>
-    <t>OSLO SSN SOSA VL</t>
+    <t>SSN SOSA VL</t>
   </si>
   <si>
     <t>https://data.vlaanderen.be/id/concept/StandaardType/Interoperabiliteit</t>
@@ -3915,6 +3915,12 @@
   </si>
   <si>
     <t>{"name":"Charter NDNN","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/charter/Werkgroep%20charter%20OSLO_NudgingDownNightNoise.pdf"}</t>
+  </si>
+  <si>
+    <t>[{"name":"OSLO SSN SOSA","resourceReference":"https://data.vlaanderen.be/standaarden/oslo-ssn-sosa-vl"},{"name":"OSLO Melding","resourceReference":"https://data.vlaanderen.be/ns/melding/"},{"name":"OSLO Verkeersmeldingen","resourceReference":"https://data.vlaanderen.be/doc/implementatiemodel/verkeersmeldingen/"},{"name":"OSLO Omgevingsvergunning","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/omgevingsvergunning/"},{"name":"OSLO Dossier","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/dossier/"},{"name":"OSLO Generiek","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/generiek-basis/"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Overzicht use cases","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-NDNN/blob/main/usecases.md"}]</t>
   </si>
 </sst>
 </file>
@@ -16792,7 +16798,7 @@
         <v>153</v>
       </c>
       <c r="F158" s="4">
-        <v>46073</v>
+        <v>46065</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>823</v>
@@ -16822,7 +16828,7 @@
         <v>46030</v>
       </c>
       <c r="P158" s="4">
-        <v>46073</v>
+        <v>46065</v>
       </c>
       <c r="Q158" s="3"/>
       <c r="R158" s="3" t="s">
@@ -16871,7 +16877,7 @@
         <v>153</v>
       </c>
       <c r="F159" s="4">
-        <v>46073</v>
+        <v>46065</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>823</v>
@@ -16901,7 +16907,7 @@
         <v>46030</v>
       </c>
       <c r="P159" s="4">
-        <v>46073</v>
+        <v>46065</v>
       </c>
       <c r="Q159" s="3"/>
       <c r="R159" s="3" t="s">
@@ -24810,10 +24816,10 @@
         <v>39</v>
       </c>
       <c r="Z258" s="3" t="s">
-        <v>34</v>
+        <v>1301</v>
       </c>
       <c r="AA258" s="3" t="s">
-        <v>34</v>
+        <v>1302</v>
       </c>
     </row>
   </sheetData>

--- a/report/merged_configurations.xlsx
+++ b/report/merged_configurations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5895" uniqueCount="1313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5870" uniqueCount="1312">
   <si>
     <t>title</t>
   </si>
@@ -254,183 +254,183 @@
     <t>[{"name":"Vocabularium VKBO - Onderneming","resourceReference":"https://implementatie.data.vlaanderen.be/ns/vkbo/onderneming"}]</t>
   </si>
   <si>
+    <t>n.v.t.</t>
+  </si>
+  <si>
+    <t>https://data.vlaanderen.be/id/concept/Domein/Economie</t>
+  </si>
+  <si>
+    <t>[{"name":"Subjectpages Onderneming","resourceReference":"https://data.vlaanderen.be/id/onderneming/"},{"name":"Subjectpages Vestiging","resourceReference":"https://data.vlaanderen.be/id/vestiging/"}]</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>[{"name":"Implementatiemodel VKBO-Onderneming","resourceReference":"https://implementatie.data.vlaanderen.be/doc/implementatiemodel/vkbo/onderneming"},{"name":"Applicatieprofiel OSLO Organisatie","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/organisatie-basis"},{"name":"Vocabularium OSLO Organisatie","resourceReference":"https://data.vlaanderen.be/ns/organisatie#"},{"name":"W3C The Organization Ontology","resourceReference":"https://www.w3.org/TR/vocab-org/"},{"name":"SEMIC Core Public Organisation Vocabulary","resourceReference":"https://semiceu.github.io/CPOV/releases/2.1.2/"},{"name":"SEMIC Core Business Vocabulary","resourceReference":"https://semiceu.github.io/Core-Business-Vocabulary/releases/2.3.0/"}]</t>
+  </si>
+  <si>
+    <t>OSLOthema-organisatie</t>
+  </si>
+  <si>
+    <t>Implementatiemodel VKBO - Onderneming</t>
+  </si>
+  <si>
+    <t>https://data.vlaanderen.be/id/concept/StandaardType/Implementatiemodel</t>
+  </si>
+  <si>
+    <t>impl-vkbo-onderneming.md</t>
+  </si>
+  <si>
+    <t>[{"name":"Implementatiemodel VKBO - Onderneming","resourceReference":"https://implementatie.data.vlaanderen.be/doc/implementatiemodel/vkbo/onderneming"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Vocabularium VKBO-Onderneming","resourceReference":"https://implementatie.data.vlaanderen.be/ns/vkbo/onderneming#"},{"name":"Applicatieprofiel OSLO Organisatie","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/organisatie-basis"},{"name":"Vocabularium OSLO Organisatie","resourceReference":"https://data.vlaanderen.be/ns/organisatie#"},{"name":"W3C The Organization Ontology","resourceReference":"https://www.w3.org/TR/vocab-org/"},{"name":"SEMIC Core Public Organisation Vocabulary","resourceReference":"https://semiceu.github.io/CPOV/releases/2.1.2/"},{"name":"SEMIC Core Business Vocabulary","resourceReference":"https://semiceu.github.io/Core-Business-Vocabulary/releases/2.3.0/"}]</t>
+  </si>
+  <si>
+    <t>Vocabularium Energiehuis</t>
+  </si>
+  <si>
+    <t>[{"name":"Energiehuis Vocabularium","resourceReference":"https://data.vlaanderen.be/ns/energiehuis"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Applicatieprofiel Energiehuis","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/energiehuis"},{"name":"Codelijst informatievoorziening thema's","resourceReference":"https://data.vlaanderen.be/id/conceptscheme/InformatievoorzieningThema"},{"name":"Codelijst adviesverlening types","resourceReference":"https://data.vlaanderen.be/id/conceptscheme/AdviesverleningType"},{"name":"Codelijst begeleiding types","resourceReference":"https://data.vlaanderen.be/id/conceptscheme/BegeleidingType"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Verslag business werkgroep - 11-09-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Business Werkgroep%20-%20Energiehuis%20-%2020240911.pdf"},{"name":"Verslag thematische werkgroep 1 - 16-10-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Thematische%20Werkgroep%201%20-%20Energiehuis%20-%2020241016.pdf"},{"name":"Verslag thematische werkgroep 2 - 14-11-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Thematische%20Werkgroep%202%20-%20Energiehuis%20-%2020241114.pdf"},{"name":"Verslag thematische werkgroep 3 - 09-12-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Thematische%20Werkgroep%203%20-%20Energiehuis%20-%2020241209.pdf"},{"name":"Verslag thematische werkgroep 4 - 16-01-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Thematische%20Werkgroep%204%20-%20Energiehuis%20-%2020250116.docx.pdf"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Presentatie business werkgroep - 11-09-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Business Werkgroep%20-%20Energiehuis%20-%2020240911.pdf"},{"name":"Presentatie thematische werkgroep 1 - 16-10-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Thematische%20Werkgroep%201%20-%20Energiehuis%20-%2020241016.pdf"},{"name":"Presentatie thematische werkgroep 2 - 14-11-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Thematische%20Werkgroep%202%20-%20Energiehuis%20-%2020241114.pdf"},{"name":"Presentatie thematische werkgroep 3 - 09-12-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Thematische%20Werkgroep%203%20-%20Energiehuis%20-%2020241209.pdf"},{"name":"Presentatie thematische werkgroep 4 - 16-01-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%204%20-%20Energiehuis%20-%2020250116.pdf"},{"name":"Presentatie Afsluitend Webinar - 14-05-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Afsluitend%20webinar%20-%20Energiehuis%20-%2020250514.pdf"}]</t>
+  </si>
+  <si>
+    <t>Vocabularium Hulp- en Dienstverlening aan Gedetineerden</t>
+  </si>
+  <si>
+    <t>[{"name":"Agentschap Justitie en Handhaving","resourceReference":"https://data.vlaanderen.be/id/organisatie/OVO049152"}]</t>
+  </si>
+  <si>
+    <t>description.md</t>
+  </si>
+  <si>
+    <t>[{"name":"Vocabularium Hulp- en Dienstverlening aan Gedetineerden","resourceReference":"https://data.vlaanderen.be/ns/hulp-dienstverlening-gedetineerden/"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Applicatieprofiel Hulp- en Dienstverlening aan Gedetineerden","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/hulp-dienstverlening-gedetineerden/"}]</t>
+  </si>
+  <si>
+    <t>Charter</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_AJH%20HDG.docx</t>
+  </si>
+  <si>
+    <t>[{"name":"Verslag business werkgroep -  30 mei 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20business%20werkgroep%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 1 -  25 juni 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%201%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 2 -  16 september 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%202%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 3 -  22 oktober 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%203%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 4 -  25 november 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%204%20-%2025%20november%202024.pdf"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Presentatie business werkgroep - 30 mei 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20business%20werkgroep%20-%20HDG.pdf"},{"name":"Presentatie thematische werkgroep 1 - 25 juni 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%201%20-%20HDG.pdf"},{"name":"Presentatie thematische werkgroep 2 - 16 september 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%202%20-%20HDG.pdf"},{"name":"Presentatie thematische werkgroep 3 - 22 oktober 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%203%20-%20HDG.pdf"},{"name":"Presentatie thematische werkgroep 4 - 25 november 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%204%20-%20HDG.pdf"}]</t>
+  </si>
+  <si>
+    <t>https://data.vlaanderen.be/id/concept/Domein/Welzijn</t>
+  </si>
+  <si>
+    <t>{"name":"Charter","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_AJH%20HDG.docx"}</t>
+  </si>
+  <si>
+    <t>Applicatieprofiel Hulp- en Dienstverlening aan Gedetineerden</t>
+  </si>
+  <si>
+    <t>[{"name":"Applicatieprofiel Hulp- en Dienstverlening aan Gedetineerden","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/hulp-dienstverlening-gedetineerden"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Business werkgroep -  30 mei 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20business%20werkgroep%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 1 -  25 juni 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%201%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 2 -  16 september 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%202%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 3 -  22 oktober 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%203%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 4 -  25 november 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%204%20-%2025%20november%202024.pdf"}]</t>
+  </si>
+  <si>
+    <t>Applicatieprofiel Erosiepoel</t>
+  </si>
+  <si>
+    <t>[{"name":"Applicatieprofiel Erosiepoel","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/erosiepoel"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Vocabularium Erosiepoel","resourceReference":"https://data.vlaanderen.be/ns/erosiepoel/"}]</t>
+  </si>
+  <si>
+    <t>https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_ModderstroomMonitoring%20-%20OSLO.docx</t>
+  </si>
+  <si>
+    <t>[{"name":"Verslag thematische werkgroep 1 -  20 juni 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/reports/ThematischeWerkgroep1.pdf"},{"name":"Verslag thematische werkgroep 2 -  6 september 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/reports/ThematischeWerkgroep2.pdf"},{"name":"Verslag thematische werkgroep 3 -  28 november 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/reports/ThematischeWerkgroep3.pdf"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Presentatie thematische werkgroep 1 - 20 juni 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/presentations/ThematischeWerkgroep1.pdf"},{"name":"Presentatie thematische werkgroep 2 - 6 september 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/presentations/ThematischeWerkgroep2.pdf"},{"name":"Presentatie thematische werkgroep 3 - 28 november 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/presentations/ThematischeWerkgroep3.pdf"}]</t>
+  </si>
+  <si>
+    <t>https://data.vlaanderen.be/id/concept/Domein/Omgeving</t>
+  </si>
+  <si>
+    <t>{"name":"Charter","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_ModderstroomMonitoring%20-%20OSLO.docx"}</t>
+  </si>
+  <si>
+    <t>Vocabularium Erosiepoel</t>
+  </si>
+  <si>
+    <t>Applicatieprofiel Mobiliteit: Intelligente Toegang</t>
+  </si>
+  <si>
+    <t>[{"name":"Applicationprofiel Mobiliteit: Intelligente Toegang","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/mobiliteit-intelligente-toegang"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Vocabularium Mobiliteit: Intelligente Toegang","resourceReference":"https://data.vlaanderen.be/doc/vocabularium/mobiliteit-intelligente-toegang"}]</t>
+  </si>
+  <si>
+    <t>Charter OSLO Citerra</t>
+  </si>
+  <si>
+    <t>https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_Citerra.docx</t>
+  </si>
+  <si>
+    <t>[{"name":"Verslag business werkgroep - 27 februari 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/reports/20240227_BW_Verslag_CoTCiterra.pdf"},{"name":"Verslag thematische werkgroep 1 - 5 juni 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/reports/20240905_ThematischeWerkgroep1_Verslag_OSLOCiterra.pdf"},{"name":"Verslag thematische werkgroep 2 -  3 oktober 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/reports/20241003_ThematischeWerkgroep2_Verslag_OSLOCiterra.pdf"},{"name":"Verslag thematische werkgroep 3 -  14 november 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/reports/20241114_ThematischeWerkgroep3_Verslag_OSLOCiterra.pdf"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Presentatie thematische werkgroep 1 - 5 juni 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/presentations/20240905_ThematicWorkshop1_Powerpoint_OSLOCiterra.pptx"},{"name":"Presentatie thematische werkgroep 2 - 3 oktober 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/presentations/20241003_ThematicWorkshop2_Powerpoint_OSLOCiterra.pptx"},{"name":"Presentatie thematische werkgroep 3 - 14 november 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/presentations/20241114_ThematicWorkshop3_Powerpoint_OSLOCiterra.pptx"}]</t>
+  </si>
+  <si>
+    <t>https://data.vlaanderen.be/id/concept/Domein/Mobiliteit</t>
+  </si>
+  <si>
+    <t>{"name":"Charter OSLO Citerra","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_Citerra.docx"}</t>
+  </si>
+  <si>
+    <t>Vocabularium Mobiliteit: Intelligente Toegang</t>
+  </si>
+  <si>
+    <t>[{"name":"Vocabularium Mobiliteit: Intelligente Toegang","resourceReference":"https://data.vlaanderen.be/ns/mobiliteit-intelligente-toegang"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Applicatieprofiel Mobiliteit: Intelligente Toegang","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/mobiliteit-intelligente-toegang"}]</t>
+  </si>
+  <si>
+    <t>Applicatieprofiel Omgevingsvergunning</t>
+  </si>
+  <si>
+    <t>[{"name":"Departement Omgeving","resourceReference":"https://data.vlaanderen.be/doc/organisatie/OVO003323"}]</t>
+  </si>
+  <si>
+    <t>omgevingsvergunning-description.md</t>
+  </si>
+  <si>
+    <t>[{"name":"Omgevingsvergunning Applicatieprofiel","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/omgevingsvergunning"}]</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/charter/Werkgroep charter OSLO_omgevingsvergunningen.pdf</t>
+  </si>
+  <si>
+    <t>[{"name":"Verslag business werkgroep - 28 augustus 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Business werkgroep Omgevingsvergunning 2023-08-28.pdf"},{"name":"Verslag thematische werkgroep 1 - 6 november 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Thematische werkgroep 1 Omgevingsvergunning 2023-11-06.pdf"},{"name":"Verslag thematische werkgroep 2 - 11 december 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Thematische werkgroep 2 Omgevingsvergunning 2023-12-11.pdf"},{"name":"Verslag thematische werkgroep 3 - 15 januari 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Thematische werkgroep 3 Omgevingsvergunning 2024-1-15.pdf"},{"name":"Verslag thematische werkgroep 4 - 19 februari 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Thematische werkgroep 4 Omgevingsvergunning 2024-2-19.pdf"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Presentatie business werkgroep - 28 augustus 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie Business Werkgroep Omgevingsvergunning 2023-08-28.pdf"},{"name":"Presentatie thematische werkgroep 1 - 6 november 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie Thematische werkgroep 1 Omgevingsvergunning 2023-11-06.pdf"},{"name":"Presentatie thematische werkgroep 2 - 11 december 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie thematische werkgroep 2 Omgevingsvergunning 2023-12-11.pdf"},{"name":"Presentatie thematische werkgroep 3 - 15 januari 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie thematische werkgroep 3 Omgevingsvergunning 2024-1-15.pdf"},{"name":"Presentatie thematische werkgroep 4 - 19 februari 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie Thematische werkgroep 4 Omgevingsvergunning 2024-2-19.pdf"}]</t>
+  </si>
+  <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>nvt</t>
-  </si>
-  <si>
-    <t>https://data.vlaanderen.be/id/concept/Domein/Economie</t>
-  </si>
-  <si>
-    <t>[{"name":"Subjectpages Onderneming","resourceReference":"https://data.vlaanderen.be/id/onderneming/"},{"name":"Subjectpages Vestiging","resourceReference":"https://data.vlaanderen.be/id/vestiging/"}]</t>
-  </si>
-  <si>
-    <t>{}</t>
-  </si>
-  <si>
-    <t>[{"name":"Implementatiemodel VKBO-Onderneming","resourceReference":"https://implementatie.data.vlaanderen.be/doc/implementatiemodel/vkbo/onderneming"},{"name":"Applicatieprofiel OSLO Organisatie","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/organisatie-basis"},{"name":"Vocabularium OSLO Organisatie","resourceReference":"https://data.vlaanderen.be/ns/organisatie#"},{"name":"W3C The Organization Ontology","resourceReference":"https://www.w3.org/TR/vocab-org/"}]</t>
-  </si>
-  <si>
-    <t>OSLOthema-organisatie</t>
-  </si>
-  <si>
-    <t>Implementatiemodel VKBO - Onderneming</t>
-  </si>
-  <si>
-    <t>https://data.vlaanderen.be/id/concept/StandaardType/Implementatiemodel</t>
-  </si>
-  <si>
-    <t>impl-vkbo-onderneming.md</t>
-  </si>
-  <si>
-    <t>[{"name":"Implementatiemodel VKBO - Onderneming","resourceReference":"https://implementatie.data.vlaanderen.be/doc/implementatiemodel/vkbo/onderneming"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Vocabularium VKBO-Onderneming","resourceReference":"https://implementatie.data.vlaanderen.be/ns/vkbo/onderneming#"},{"name":"Applicatieprofiel OSLO Organisatie","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/organisatie-basis"},{"name":"Vocabularium OSLO Organisatie","resourceReference":"https://data.vlaanderen.be/ns/organisatie#"},{"name":"W3C The Organization Ontology","resourceReference":"https://www.w3.org/TR/vocab-org/"}]</t>
-  </si>
-  <si>
-    <t>Vocabularium Energiehuis</t>
-  </si>
-  <si>
-    <t>[{"name":"Energiehuis Vocabularium","resourceReference":"https://data.vlaanderen.be/ns/energiehuis"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Applicatieprofiel Energiehuis","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/energiehuis"},{"name":"Codelijst informatievoorziening thema's","resourceReference":"https://data.vlaanderen.be/id/conceptscheme/InformatievoorzieningThema"},{"name":"Codelijst adviesverlening types","resourceReference":"https://data.vlaanderen.be/id/conceptscheme/AdviesverleningType"},{"name":"Codelijst begeleiding types","resourceReference":"https://data.vlaanderen.be/id/conceptscheme/BegeleidingType"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Verslag business werkgroep - 11-09-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Business Werkgroep%20-%20Energiehuis%20-%2020240911.pdf"},{"name":"Verslag thematische werkgroep 1 - 16-10-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Thematische%20Werkgroep%201%20-%20Energiehuis%20-%2020241016.pdf"},{"name":"Verslag thematische werkgroep 2 - 14-11-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Thematische%20Werkgroep%202%20-%20Energiehuis%20-%2020241114.pdf"},{"name":"Verslag thematische werkgroep 3 - 09-12-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Thematische%20Werkgroep%203%20-%20Energiehuis%20-%2020241209.pdf"},{"name":"Verslag thematische werkgroep 4 - 16-01-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/reports/Verslag%20-%20Thematische%20Werkgroep%204%20-%20Energiehuis%20-%2020250116.docx.pdf"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Presentatie business werkgroep - 11-09-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Business Werkgroep%20-%20Energiehuis%20-%2020240911.pdf"},{"name":"Presentatie thematische werkgroep 1 - 16-10-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Thematische%20Werkgroep%201%20-%20Energiehuis%20-%2020241016.pdf"},{"name":"Presentatie thematische werkgroep 2 - 14-11-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Thematische%20Werkgroep%202%20-%20Energiehuis%20-%2020241114.pdf"},{"name":"Presentatie thematische werkgroep 3 - 09-12-2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Thematische%20Werkgroep%203%20-%20Energiehuis%20-%2020241209.pdf"},{"name":"Presentatie thematische werkgroep 4 - 16-01-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%204%20-%20Energiehuis%20-%2020250116.pdf"},{"name":"Presentatie Afsluitend Webinar - 14-05-2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-energiehuis/standaardenregister/presentations/Presentatie%20-%20Afsluitend%20webinar%20-%20Energiehuis%20-%2020250514.pdf"}]</t>
-  </si>
-  <si>
-    <t>Vocabularium Hulp- en Dienstverlening aan Gedetineerden</t>
-  </si>
-  <si>
-    <t>[{"name":"Agentschap Justitie en Handhaving","resourceReference":"https://data.vlaanderen.be/id/organisatie/OVO049152"}]</t>
-  </si>
-  <si>
-    <t>description.md</t>
-  </si>
-  <si>
-    <t>[{"name":"Vocabularium Hulp- en Dienstverlening aan Gedetineerden","resourceReference":"https://data.vlaanderen.be/ns/hulp-dienstverlening-gedetineerden/"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Applicatieprofiel Hulp- en Dienstverlening aan Gedetineerden","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/hulp-dienstverlening-gedetineerden/"}]</t>
-  </si>
-  <si>
-    <t>Charter</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_AJH%20HDG.docx</t>
-  </si>
-  <si>
-    <t>[{"name":"Verslag business werkgroep -  30 mei 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20business%20werkgroep%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 1 -  25 juni 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%201%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 2 -  16 september 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%202%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 3 -  22 oktober 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%203%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 4 -  25 november 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%204%20-%2025%20november%202024.pdf"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Presentatie business werkgroep - 30 mei 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20business%20werkgroep%20-%20HDG.pdf"},{"name":"Presentatie thematische werkgroep 1 - 25 juni 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%201%20-%20HDG.pdf"},{"name":"Presentatie thematische werkgroep 2 - 16 september 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%202%20-%20HDG.pdf"},{"name":"Presentatie thematische werkgroep 3 - 22 oktober 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%203%20-%20HDG.pdf"},{"name":"Presentatie thematische werkgroep 4 - 25 november 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/presentations/Presentatie%20thematische%20werkgroep%204%20-%20HDG.pdf"}]</t>
-  </si>
-  <si>
-    <t>https://data.vlaanderen.be/id/concept/Domein/Welzijn</t>
-  </si>
-  <si>
-    <t>{"name":"Charter","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_AJH%20HDG.docx"}</t>
-  </si>
-  <si>
-    <t>Applicatieprofiel Hulp- en Dienstverlening aan Gedetineerden</t>
-  </si>
-  <si>
-    <t>[{"name":"Applicatieprofiel Hulp- en Dienstverlening aan Gedetineerden","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/hulp-dienstverlening-gedetineerden"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Business werkgroep -  30 mei 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20business%20werkgroep%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 1 -  25 juni 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%201%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 2 -  16 september 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%202%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 3 -  22 oktober 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%203%20-%20HDG.pdf"},{"name":"Verslag thematische werkgroep 4 -  25 november 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-hulpEnDienstverleningAanGedetineerden/blob/standaardenregister/reports/Verslag%20thematische%20werkgroep%204%20-%2025%20november%202024.pdf"}]</t>
-  </si>
-  <si>
-    <t>Applicatieprofiel Erosiepoel</t>
-  </si>
-  <si>
-    <t>[{"name":"Applicatieprofiel Erosiepoel","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/erosiepoel"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Vocabularium Erosiepoel","resourceReference":"https://data.vlaanderen.be/ns/erosiepoel/"}]</t>
-  </si>
-  <si>
-    <t>https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_ModderstroomMonitoring%20-%20OSLO.docx</t>
-  </si>
-  <si>
-    <t>[{"name":"Verslag thematische werkgroep 1 -  20 juni 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/reports/ThematischeWerkgroep1.pdf"},{"name":"Verslag thematische werkgroep 2 -  6 september 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/reports/ThematischeWerkgroep2.pdf"},{"name":"Verslag thematische werkgroep 3 -  28 november 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/reports/ThematischeWerkgroep3.pdf"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Presentatie thematische werkgroep 1 - 20 juni 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/presentations/ThematischeWerkgroep1.pdf"},{"name":"Presentatie thematische werkgroep 2 - 6 september 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/presentations/ThematischeWerkgroep2.pdf"},{"name":"Presentatie thematische werkgroep 3 - 28 november 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/presentations/ThematischeWerkgroep3.pdf"}]</t>
-  </si>
-  <si>
-    <t>https://data.vlaanderen.be/id/concept/Domein/Omgeving</t>
-  </si>
-  <si>
-    <t>{"name":"Charter","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-modderstromen/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_ModderstroomMonitoring%20-%20OSLO.docx"}</t>
-  </si>
-  <si>
-    <t>Vocabularium Erosiepoel</t>
-  </si>
-  <si>
-    <t>Applicatieprofiel Mobiliteit: Intelligente Toegang</t>
-  </si>
-  <si>
-    <t>[{"name":"Applicationprofiel Mobiliteit: Intelligente Toegang","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/mobiliteit-intelligente-toegang"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Vocabularium Mobiliteit: Intelligente Toegang","resourceReference":"https://data.vlaanderen.be/doc/vocabularium/mobiliteit-intelligente-toegang"}]</t>
-  </si>
-  <si>
-    <t>Charter OSLO Citerra</t>
-  </si>
-  <si>
-    <t>https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_Citerra.docx</t>
-  </si>
-  <si>
-    <t>[{"name":"Verslag business werkgroep - 27 februari 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/reports/20240227_BW_Verslag_CoTCiterra.pdf"},{"name":"Verslag thematische werkgroep 1 - 5 juni 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/reports/20240905_ThematischeWerkgroep1_Verslag_OSLOCiterra.pdf"},{"name":"Verslag thematische werkgroep 2 -  3 oktober 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/reports/20241003_ThematischeWerkgroep2_Verslag_OSLOCiterra.pdf"},{"name":"Verslag thematische werkgroep 3 -  14 november 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/reports/20241114_ThematischeWerkgroep3_Verslag_OSLOCiterra.pdf"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Presentatie thematische werkgroep 1 - 5 juni 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/presentations/20240905_ThematicWorkshop1_Powerpoint_OSLOCiterra.pptx"},{"name":"Presentatie thematische werkgroep 2 - 3 oktober 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/presentations/20241003_ThematicWorkshop2_Powerpoint_OSLOCiterra.pptx"},{"name":"Presentatie thematische werkgroep 3 - 14 november 2024","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/presentations/20241114_ThematicWorkshop3_Powerpoint_OSLOCiterra.pptx"}]</t>
-  </si>
-  <si>
-    <t>https://data.vlaanderen.be/id/concept/Domein/Mobiliteit</t>
-  </si>
-  <si>
-    <t>{"name":"Charter OSLO Citerra","resourceReference":"https://github.com/Informatievlaanderen/OSLOthema-citerra/blob/standaardenregister/charter/Werkgroep%20charter%20OSLO_Citerra.docx"}</t>
-  </si>
-  <si>
-    <t>Vocabularium Mobiliteit: Intelligente Toegang</t>
-  </si>
-  <si>
-    <t>[{"name":"Vocabularium Mobiliteit: Intelligente Toegang","resourceReference":"https://data.vlaanderen.be/ns/mobiliteit-intelligente-toegang"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Applicatieprofiel Mobiliteit: Intelligente Toegang","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/mobiliteit-intelligente-toegang"}]</t>
-  </si>
-  <si>
-    <t>Applicatieprofiel Omgevingsvergunning</t>
-  </si>
-  <si>
-    <t>[{"name":"Departement Omgeving","resourceReference":"https://data.vlaanderen.be/doc/organisatie/OVO003323"}]</t>
-  </si>
-  <si>
-    <t>omgevingsvergunning-description.md</t>
-  </si>
-  <si>
-    <t>[{"name":"Omgevingsvergunning Applicatieprofiel","resourceReference":"https://data.vlaanderen.be/doc/applicatieprofiel/omgevingsvergunning"}]</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/charter/Werkgroep charter OSLO_omgevingsvergunningen.pdf</t>
-  </si>
-  <si>
-    <t>[{"name":"Verslag business werkgroep - 28 augustus 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Business werkgroep Omgevingsvergunning 2023-08-28.pdf"},{"name":"Verslag thematische werkgroep 1 - 6 november 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Thematische werkgroep 1 Omgevingsvergunning 2023-11-06.pdf"},{"name":"Verslag thematische werkgroep 2 - 11 december 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Thematische werkgroep 2 Omgevingsvergunning 2023-12-11.pdf"},{"name":"Verslag thematische werkgroep 3 - 15 januari 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Thematische werkgroep 3 Omgevingsvergunning 2024-1-15.pdf"},{"name":"Verslag thematische werkgroep 4 - 19 februari 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/reports/Verslag Thematische werkgroep 4 Omgevingsvergunning 2024-2-19.pdf"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Presentatie business werkgroep - 28 augustus 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie Business Werkgroep Omgevingsvergunning 2023-08-28.pdf"},{"name":"Presentatie thematische werkgroep 1 - 6 november 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie Thematische werkgroep 1 Omgevingsvergunning 2023-11-06.pdf"},{"name":"Presentatie thematische werkgroep 2 - 11 december 2023","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie thematische werkgroep 2 Omgevingsvergunning 2023-12-11.pdf"},{"name":"Presentatie thematische werkgroep 3 - 15 januari 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie thematische werkgroep 3 Omgevingsvergunning 2024-1-15.pdf"},{"name":"Presentatie thematische werkgroep 4 - 19 februari 2024","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/presentations/Presentatie Thematische werkgroep 4 Omgevingsvergunning 2024-2-19.pdf"}]</t>
-  </si>
-  <si>
     <t>{"name":"Charter","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-omgevingsvergunning/standaardenregister/charter/Werkgroep charter OSLO_omgevingsvergunningen.pdf"}</t>
   </si>
   <si>
@@ -3596,9 +3596,6 @@
     <t>OSLOthema-kindFiche</t>
   </si>
   <si>
-    <t>Vocabularium Kindfiche</t>
-  </si>
-  <si>
     <t>Vocabularium OSLO Statistiek</t>
   </si>
   <si>
@@ -3911,10 +3908,10 @@
     <t>https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/charter/Charter_OSLO_SSN%20SOSA%20VL.docx</t>
   </si>
   <si>
-    <t>[{"name":"Verslag Business Werkgroep - 3 december 2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/reports/Verslag%20-%20Business%20werkgroep%20SSN%20SOSA%20VL.pdf"},{"name":"Verslag Thematische Werkgroep 1 - 14 januari 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/reports/Verslag%20Thematische%20werkgroep%201%20-%20SSN%20SOSA%20%202026-02-02.pdf"},{"name":"Verslag Thematische Werkgroep 2 - 3 april 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/reports/Verslag%20Thematische%20werkgroep%202%20-%20SSN%20SOSA%20%202026-03-04.pdf"}]</t>
-  </si>
-  <si>
-    <t>[{"name":"Presentatie Business Werkgroep -  3 december 2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/presentations/SSN%20SOSA%20VL%20Business%20Werkgroep.pdf"},{"name":"Presentatie Thematische Werkgroep 1 - 14 januari 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/presentations/Presentatie%20SSN%20SOSA%20VL%20Thematische%20werkgroep%201.pdf"},{"name":"Presentatie Thematische Werkgroep 2 - 3 april 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/presentations/Presentatie%20SSN%20SOSA%20VL%20Thematische%20werkgroep%202.pdf"}]</t>
+    <t>[{"name":"Verslag Business Werkgroep - 3 december 2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/reports/Verslag%20-%20Business%20werkgroep%20SSN%20SOSA%20VL.pdf"},{"name":"Verslag Thematische Werkgroep 1 - 14 januari 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/reports/Verslag%20Thematische%20werkgroep%201%20-%20SSN%20SOSA%20%202026-02-02.pdf"},{"name":"Verslag Thematische Werkgroep 2 - 3 april 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/reports/Verslag%20Thematische%20werkgroep%202%20-%20SSN%20SOSA%20%202026-03-04.pdf"},{"name":"Verslag Thematische Werkgroep 3 - 29 april 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/reports/Verslag%20Thematische%20werkgroep%203%20-%20SSN%20SOSA%20%202026-29-04.pdf"}]</t>
+  </si>
+  <si>
+    <t>[{"name":"Presentatie Business Werkgroep -  3 december 2025","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/presentations/SSN%20SOSA%20VL%20Business%20Werkgroep.pdf"},{"name":"Presentatie Thematische Werkgroep 1 - 14 januari 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/presentations/Presentatie%20SSN%20SOSA%20VL%20Thematische%20werkgroep%201.pdf"},{"name":"Presentatie Thematische Werkgroep 2 - 3 april 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/presentations/Presentatie%20SSN%20SOSA%20VL%20Thematische%20werkgroep%202.pdf"},{"name":"Presentatie Thematische Werkgroep 3 - 29 april 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-SSNSOSA-VL/standaardenregister/presentations/Presentatie%20SSN%20SOSA%20VL%20Thematische%20werkgroep%203.pdf"}]</t>
   </si>
   <si>
     <t>https://data.vlaanderen.be/doc/concept/Domein/Omgeving</t>
@@ -4358,7 +4355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA260"/>
+  <dimension ref="A1:AA259"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="27" width="44" customWidth="1"/>
@@ -4614,7 +4611,7 @@
         <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>54</v>
@@ -4811,34 +4808,34 @@
         <v>80</v>
       </c>
       <c r="Q6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="T6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="R6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="T6" s="3" t="s">
+      <c r="U6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="V6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="V6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W6" s="3" t="s">
+      <c r="X6" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AA6" s="3" t="s">
         <v>39</v>
@@ -4846,10 +4843,10 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>29</v>
@@ -4864,10 +4861,10 @@
         <v>46184</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>34</v>
@@ -4894,34 +4891,34 @@
         <v>80</v>
       </c>
       <c r="Q7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="T7" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="R7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="T7" s="3" t="s">
+      <c r="U7" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="U7" s="3" t="s">
+      <c r="V7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="V7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="X7" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Z7" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AA7" s="3" t="s">
         <v>39</v>
@@ -4929,7 +4926,7 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>76</v>
@@ -4950,10 +4947,10 @@
         <v>66</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>69</v>
@@ -4962,10 +4959,10 @@
         <v>70</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="N8" s="4">
         <v>45428</v>
@@ -5010,7 +5007,7 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>76</v>
@@ -5022,31 +5019,31 @@
         <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F9" s="4">
         <v>45856</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="N9" s="4">
         <v>45625</v>
@@ -5065,16 +5062,16 @@
       </c>
       <c r="S9" s="3"/>
       <c r="T9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>39</v>
@@ -5091,7 +5088,7 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>28</v>
@@ -5103,31 +5100,31 @@
         <v>42</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F10" s="4">
         <v>45856</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="J10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="M10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N10" s="4">
         <v>45625</v>
@@ -5146,16 +5143,16 @@
       </c>
       <c r="S10" s="3"/>
       <c r="T10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W10" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>39</v>
@@ -5172,7 +5169,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>28</v>
@@ -5190,25 +5187,25 @@
         <v>45861</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -5223,16 +5220,16 @@
       </c>
       <c r="S11" s="3"/>
       <c r="T11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W11" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="X11" s="3" t="s">
         <v>39</v>
@@ -5249,7 +5246,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>76</v>
@@ -5267,25 +5264,25 @@
         <v>45861</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
@@ -5300,16 +5297,16 @@
       </c>
       <c r="S12" s="3"/>
       <c r="T12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W12" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>39</v>
@@ -5326,7 +5323,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>28</v>
@@ -5344,25 +5341,25 @@
         <v>45604</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="4">
@@ -5375,16 +5372,16 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W13" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="X13" s="3" t="s">
         <v>39</v>
@@ -5401,7 +5398,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>76</v>
@@ -5419,25 +5416,25 @@
         <v>45604</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="4">
@@ -5450,16 +5447,16 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W14" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>39</v>
@@ -5476,7 +5473,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>28</v>
@@ -5488,31 +5485,31 @@
         <v>42</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F15" s="4">
         <v>45603</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K15" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="N15" s="4">
         <v>45169</v>
@@ -5521,7 +5518,7 @@
         <v>45603</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3" t="s">
@@ -5529,7 +5526,7 @@
       </c>
       <c r="S15" s="3"/>
       <c r="T15" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>39</v>
@@ -5567,13 +5564,13 @@
         <v>42</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F16" s="4">
         <v>45603</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>142</v>
@@ -5582,16 +5579,16 @@
         <v>34</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="N16" s="4">
         <v>45169</v>
@@ -5600,7 +5597,7 @@
         <v>45603</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
@@ -5608,7 +5605,7 @@
       </c>
       <c r="S16" s="3"/>
       <c r="T16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U16" s="3" t="s">
         <v>39</v>
@@ -5821,7 +5818,7 @@
         <v>34</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>158</v>
@@ -5836,10 +5833,10 @@
         <v>44974</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3" t="s">
@@ -5900,7 +5897,7 @@
         <v>34</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>158</v>
@@ -5915,10 +5912,10 @@
         <v>44974</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3" t="s">
@@ -5994,10 +5991,10 @@
         <v>44147</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3" t="s">
@@ -6005,7 +6002,7 @@
       </c>
       <c r="S21" s="3"/>
       <c r="T21" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>39</v>
@@ -6073,10 +6070,10 @@
         <v>44147</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3" t="s">
@@ -6084,7 +6081,7 @@
       </c>
       <c r="S22" s="3"/>
       <c r="T22" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>39</v>
@@ -6165,7 +6162,7 @@
       </c>
       <c r="S23" s="3"/>
       <c r="T23" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>39</v>
@@ -6246,7 +6243,7 @@
       </c>
       <c r="S24" s="3"/>
       <c r="T24" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>39</v>
@@ -6299,7 +6296,7 @@
         <v>34</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>194</v>
@@ -6314,10 +6311,10 @@
         <v>44974</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3" t="s">
@@ -6408,7 +6405,7 @@
         <v>45350</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>39</v>
@@ -6570,7 +6567,7 @@
       </c>
       <c r="S28" s="3"/>
       <c r="T28" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U28" s="3" t="s">
         <v>39</v>
@@ -6649,7 +6646,7 @@
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>39</v>
@@ -6860,7 +6857,7 @@
         <v>249</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>250</v>
@@ -6875,10 +6872,10 @@
         <v>44000</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3" t="s">
@@ -6886,7 +6883,7 @@
       </c>
       <c r="S32" s="3"/>
       <c r="T32" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>39</v>
@@ -6939,7 +6936,7 @@
         <v>257</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>250</v>
@@ -6954,10 +6951,10 @@
         <v>44000</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
@@ -6965,7 +6962,7 @@
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>39</v>
@@ -7018,7 +7015,7 @@
         <v>261</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>250</v>
@@ -7033,10 +7030,10 @@
         <v>44000</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q34" s="4">
         <v>45566</v>
@@ -7046,7 +7043,7 @@
       </c>
       <c r="S34" s="3"/>
       <c r="T34" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U34" s="3" t="s">
         <v>39</v>
@@ -7099,7 +7096,7 @@
         <v>265</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>250</v>
@@ -7114,10 +7111,10 @@
         <v>44000</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="4">
         <v>45566</v>
@@ -7127,7 +7124,7 @@
       </c>
       <c r="S35" s="3"/>
       <c r="T35" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>39</v>
@@ -7180,7 +7177,7 @@
         <v>269</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>250</v>
@@ -7195,10 +7192,10 @@
         <v>44000</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="4">
         <v>45566</v>
@@ -7208,7 +7205,7 @@
       </c>
       <c r="S36" s="3"/>
       <c r="T36" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U36" s="3" t="s">
         <v>39</v>
@@ -7261,7 +7258,7 @@
         <v>273</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>250</v>
@@ -7276,10 +7273,10 @@
         <v>44000</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="4">
         <v>45566</v>
@@ -7289,7 +7286,7 @@
       </c>
       <c r="S37" s="3"/>
       <c r="T37" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U37" s="3" t="s">
         <v>39</v>
@@ -7342,7 +7339,7 @@
         <v>276</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>250</v>
@@ -7357,10 +7354,10 @@
         <v>44000</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q38" s="4">
         <v>45566</v>
@@ -7370,7 +7367,7 @@
       </c>
       <c r="S38" s="3"/>
       <c r="T38" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U38" s="3" t="s">
         <v>39</v>
@@ -7423,7 +7420,7 @@
         <v>279</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>250</v>
@@ -7438,10 +7435,10 @@
         <v>44000</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q39" s="4">
         <v>45566</v>
@@ -7451,7 +7448,7 @@
       </c>
       <c r="S39" s="3"/>
       <c r="T39" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U39" s="3" t="s">
         <v>39</v>
@@ -7504,7 +7501,7 @@
         <v>283</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>250</v>
@@ -7519,10 +7516,10 @@
         <v>44000</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q40" s="4">
         <v>45566</v>
@@ -7532,7 +7529,7 @@
       </c>
       <c r="S40" s="3"/>
       <c r="T40" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>39</v>
@@ -7585,7 +7582,7 @@
         <v>287</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>250</v>
@@ -7600,10 +7597,10 @@
         <v>44000</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q41" s="4">
         <v>45566</v>
@@ -7613,7 +7610,7 @@
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>39</v>
@@ -7666,7 +7663,7 @@
         <v>290</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>250</v>
@@ -7681,10 +7678,10 @@
         <v>44000</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="3" t="s">
@@ -7692,7 +7689,7 @@
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>39</v>
@@ -7745,7 +7742,7 @@
         <v>292</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>250</v>
@@ -7760,10 +7757,10 @@
         <v>44000</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q43" s="3"/>
       <c r="R43" s="3" t="s">
@@ -7771,7 +7768,7 @@
       </c>
       <c r="S43" s="3"/>
       <c r="T43" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>39</v>
@@ -7824,7 +7821,7 @@
         <v>296</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>250</v>
@@ -7842,7 +7839,7 @@
         <v>45603</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q44" s="4">
         <v>45566</v>
@@ -7852,7 +7849,7 @@
       </c>
       <c r="S44" s="3"/>
       <c r="T44" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>39</v>
@@ -7905,7 +7902,7 @@
         <v>300</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>250</v>
@@ -7923,7 +7920,7 @@
         <v>45603</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q45" s="4">
         <v>45566</v>
@@ -7933,7 +7930,7 @@
       </c>
       <c r="S45" s="3"/>
       <c r="T45" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>39</v>
@@ -7986,7 +7983,7 @@
         <v>303</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>250</v>
@@ -8001,10 +7998,10 @@
         <v>44000</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q46" s="3"/>
       <c r="R46" s="3" t="s">
@@ -8012,7 +8009,7 @@
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>39</v>
@@ -8065,7 +8062,7 @@
         <v>306</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>250</v>
@@ -8080,10 +8077,10 @@
         <v>44000</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q47" s="3"/>
       <c r="R47" s="3" t="s">
@@ -8091,7 +8088,7 @@
       </c>
       <c r="S47" s="3"/>
       <c r="T47" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>39</v>
@@ -8144,7 +8141,7 @@
         <v>310</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>250</v>
@@ -8162,7 +8159,7 @@
         <v>45603</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q48" s="4">
         <v>45566</v>
@@ -8172,7 +8169,7 @@
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>39</v>
@@ -8225,7 +8222,7 @@
         <v>314</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>250</v>
@@ -8243,7 +8240,7 @@
         <v>45603</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q49" s="4">
         <v>45566</v>
@@ -8253,7 +8250,7 @@
       </c>
       <c r="S49" s="3"/>
       <c r="T49" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>39</v>
@@ -8306,7 +8303,7 @@
         <v>318</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>250</v>
@@ -8324,7 +8321,7 @@
         <v>45603</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q50" s="4">
         <v>45566</v>
@@ -8334,7 +8331,7 @@
       </c>
       <c r="S50" s="3"/>
       <c r="T50" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U50" s="3" t="s">
         <v>39</v>
@@ -8387,7 +8384,7 @@
         <v>322</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>250</v>
@@ -8405,7 +8402,7 @@
         <v>45603</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q51" s="4">
         <v>45566</v>
@@ -8415,7 +8412,7 @@
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U51" s="3" t="s">
         <v>39</v>
@@ -8644,7 +8641,7 @@
         <v>44637</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="4">
@@ -8723,7 +8720,7 @@
         <v>44637</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="4">
@@ -8799,10 +8796,10 @@
         <v>44287</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q56" s="3"/>
       <c r="R56" s="3" t="s">
@@ -8878,10 +8875,10 @@
         <v>44287</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q57" s="3"/>
       <c r="R57" s="3" t="s">
@@ -8968,7 +8965,7 @@
       </c>
       <c r="S58" s="3"/>
       <c r="T58" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>39</v>
@@ -9047,7 +9044,7 @@
       </c>
       <c r="S59" s="3"/>
       <c r="T59" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>39</v>
@@ -9126,7 +9123,7 @@
       </c>
       <c r="S60" s="3"/>
       <c r="T60" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>39</v>
@@ -9205,7 +9202,7 @@
       </c>
       <c r="S61" s="3"/>
       <c r="T61" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U61" s="3" t="s">
         <v>39</v>
@@ -9352,10 +9349,10 @@
         <v>43200</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q63" s="3"/>
       <c r="R63" s="3" t="s">
@@ -9442,7 +9439,7 @@
       </c>
       <c r="S64" s="3"/>
       <c r="T64" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U64" s="3" t="s">
         <v>39</v>
@@ -9513,7 +9510,7 @@
         <v>43377</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q65" s="3"/>
       <c r="R65" s="3" t="s">
@@ -9521,7 +9518,7 @@
       </c>
       <c r="S65" s="3"/>
       <c r="T65" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U65" s="3" t="s">
         <v>39</v>
@@ -9826,10 +9823,10 @@
         <v>424</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q69" s="3"/>
       <c r="R69" s="3" t="s">
@@ -10013,7 +10010,7 @@
         <v>39</v>
       </c>
       <c r="Z71" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AA71" s="3" t="s">
         <v>39</v>
@@ -10063,10 +10060,10 @@
         <v>43200</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q72" s="3"/>
       <c r="R72" s="3" t="s">
@@ -10092,7 +10089,7 @@
         <v>39</v>
       </c>
       <c r="Z72" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>39</v>
@@ -10103,13 +10100,13 @@
         <v>451</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>452</v>
@@ -10166,7 +10163,7 @@
         <v>39</v>
       </c>
       <c r="W73" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X73" s="3" t="s">
         <v>39</v>
@@ -10184,13 +10181,13 @@
         <v>451</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>452</v>
@@ -10247,7 +10244,7 @@
         <v>39</v>
       </c>
       <c r="W74" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X74" s="3" t="s">
         <v>39</v>
@@ -10462,10 +10459,10 @@
         <v>43200</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q77" s="3"/>
       <c r="R77" s="3" t="s">
@@ -10473,7 +10470,7 @@
       </c>
       <c r="S77" s="3"/>
       <c r="T77" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U77" s="3" t="s">
         <v>39</v>
@@ -10552,7 +10549,7 @@
       </c>
       <c r="S78" s="3"/>
       <c r="T78" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U78" s="3" t="s">
         <v>39</v>
@@ -10623,7 +10620,7 @@
         <v>43412</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q79" s="3"/>
       <c r="R79" s="3" t="s">
@@ -10631,7 +10628,7 @@
       </c>
       <c r="S79" s="3"/>
       <c r="T79" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U79" s="3" t="s">
         <v>39</v>
@@ -10699,10 +10696,10 @@
         <v>43200</v>
       </c>
       <c r="O80" s="4">
-        <v>43412</v>
-      </c>
-      <c r="P80" s="3" t="s">
-        <v>80</v>
+        <v>43249</v>
+      </c>
+      <c r="P80" s="4">
+        <v>43284</v>
       </c>
       <c r="Q80" s="3"/>
       <c r="R80" s="3" t="s">
@@ -10710,7 +10707,7 @@
       </c>
       <c r="S80" s="3"/>
       <c r="T80" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U80" s="3" t="s">
         <v>39</v>
@@ -10778,10 +10775,10 @@
         <v>2019</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q81" s="3"/>
       <c r="R81" s="3" t="s">
@@ -10789,7 +10786,7 @@
       </c>
       <c r="S81" s="3"/>
       <c r="T81" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>39</v>
@@ -11252,7 +11249,7 @@
         <v>43538</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P87" s="4">
         <v>45194</v>
@@ -11331,7 +11328,7 @@
         <v>43538</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P88" s="4">
         <v>45194</v>
@@ -11410,10 +11407,10 @@
         <v>43405</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q89" s="3"/>
       <c r="R89" s="3" t="s">
@@ -11489,10 +11486,10 @@
         <v>43405</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q90" s="3"/>
       <c r="R90" s="3" t="s">
@@ -11579,7 +11576,7 @@
       </c>
       <c r="S91" s="3"/>
       <c r="T91" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>39</v>
@@ -11658,7 +11655,7 @@
       </c>
       <c r="S92" s="3"/>
       <c r="T92" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U92" s="3" t="s">
         <v>39</v>
@@ -11737,7 +11734,7 @@
       </c>
       <c r="S93" s="3"/>
       <c r="T93" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U93" s="3" t="s">
         <v>39</v>
@@ -11816,7 +11813,7 @@
       </c>
       <c r="S94" s="3"/>
       <c r="T94" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>39</v>
@@ -12211,7 +12208,7 @@
       </c>
       <c r="S99" s="3"/>
       <c r="T99" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U99" s="3" t="s">
         <v>39</v>
@@ -12290,7 +12287,7 @@
       </c>
       <c r="S100" s="3"/>
       <c r="T100" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>39</v>
@@ -12369,7 +12366,7 @@
       </c>
       <c r="S101" s="3"/>
       <c r="T101" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>39</v>
@@ -12448,7 +12445,7 @@
       </c>
       <c r="S102" s="3"/>
       <c r="T102" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>39</v>
@@ -13159,7 +13156,7 @@
       </c>
       <c r="S111" s="3"/>
       <c r="T111" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U111" s="3" t="s">
         <v>39</v>
@@ -13238,7 +13235,7 @@
       </c>
       <c r="S112" s="3"/>
       <c r="T112" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U112" s="3" t="s">
         <v>39</v>
@@ -13317,7 +13314,7 @@
       </c>
       <c r="S113" s="3"/>
       <c r="T113" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U113" s="3" t="s">
         <v>39</v>
@@ -13396,7 +13393,7 @@
       </c>
       <c r="S114" s="3"/>
       <c r="T114" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U114" s="3" t="s">
         <v>39</v>
@@ -13475,7 +13472,7 @@
       </c>
       <c r="S115" s="3"/>
       <c r="T115" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U115" s="3" t="s">
         <v>39</v>
@@ -13554,7 +13551,7 @@
       </c>
       <c r="S116" s="3"/>
       <c r="T116" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U116" s="3" t="s">
         <v>39</v>
@@ -13633,7 +13630,7 @@
       </c>
       <c r="S117" s="3"/>
       <c r="T117" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U117" s="3" t="s">
         <v>39</v>
@@ -13712,7 +13709,7 @@
       </c>
       <c r="S118" s="3"/>
       <c r="T118" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U118" s="3" t="s">
         <v>39</v>
@@ -13791,7 +13788,7 @@
       </c>
       <c r="S119" s="3"/>
       <c r="T119" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U119" s="3" t="s">
         <v>39</v>
@@ -13870,7 +13867,7 @@
       </c>
       <c r="S120" s="3"/>
       <c r="T120" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U120" s="3" t="s">
         <v>39</v>
@@ -13949,7 +13946,7 @@
       </c>
       <c r="S121" s="3"/>
       <c r="T121" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U121" s="3" t="s">
         <v>39</v>
@@ -14028,7 +14025,7 @@
       </c>
       <c r="S122" s="3"/>
       <c r="T122" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U122" s="3" t="s">
         <v>39</v>
@@ -14107,7 +14104,7 @@
       </c>
       <c r="S123" s="3"/>
       <c r="T123" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U123" s="3" t="s">
         <v>39</v>
@@ -14186,7 +14183,7 @@
       </c>
       <c r="S124" s="3"/>
       <c r="T124" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U124" s="3" t="s">
         <v>39</v>
@@ -14265,7 +14262,7 @@
       </c>
       <c r="S125" s="3"/>
       <c r="T125" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U125" s="3" t="s">
         <v>39</v>
@@ -14344,7 +14341,7 @@
       </c>
       <c r="S126" s="3"/>
       <c r="T126" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U126" s="3" t="s">
         <v>39</v>
@@ -14412,10 +14409,10 @@
         <v>2018</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P127" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q127" s="3"/>
       <c r="R127" s="3" t="s">
@@ -14423,7 +14420,7 @@
       </c>
       <c r="S127" s="3"/>
       <c r="T127" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U127" s="3" t="s">
         <v>39</v>
@@ -14847,7 +14844,7 @@
         <v>755</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>29</v>
@@ -14886,10 +14883,10 @@
         <v>45540</v>
       </c>
       <c r="O133" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P133" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q133" s="4">
         <v>45743</v>
@@ -14967,10 +14964,10 @@
         <v>43249</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P134" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q134" s="3"/>
       <c r="R134" s="3" t="s">
@@ -14978,7 +14975,7 @@
       </c>
       <c r="S134" s="3"/>
       <c r="T134" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U134" s="3" t="s">
         <v>39</v>
@@ -15046,10 +15043,10 @@
         <v>43249</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P135" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q135" s="3"/>
       <c r="R135" s="3" t="s">
@@ -15057,7 +15054,7 @@
       </c>
       <c r="S135" s="3"/>
       <c r="T135" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U135" s="3" t="s">
         <v>39</v>
@@ -15120,13 +15117,13 @@
         <v>34</v>
       </c>
       <c r="N136" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P136" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q136" s="3"/>
       <c r="R136" s="3" t="s">
@@ -15290,7 +15287,7 @@
       </c>
       <c r="S138" s="3"/>
       <c r="T138" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U138" s="3" t="s">
         <v>39</v>
@@ -15369,7 +15366,7 @@
       </c>
       <c r="S139" s="3"/>
       <c r="T139" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U139" s="3" t="s">
         <v>39</v>
@@ -15448,7 +15445,7 @@
       </c>
       <c r="S140" s="3"/>
       <c r="T140" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U140" s="3" t="s">
         <v>39</v>
@@ -15527,7 +15524,7 @@
       </c>
       <c r="S141" s="3"/>
       <c r="T141" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U141" s="3" t="s">
         <v>39</v>
@@ -15606,7 +15603,7 @@
       </c>
       <c r="S142" s="3"/>
       <c r="T142" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U142" s="3" t="s">
         <v>39</v>
@@ -15685,7 +15682,7 @@
       </c>
       <c r="S143" s="3"/>
       <c r="T143" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U143" s="3" t="s">
         <v>39</v>
@@ -15764,7 +15761,7 @@
       </c>
       <c r="S144" s="3"/>
       <c r="T144" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U144" s="3" t="s">
         <v>39</v>
@@ -15843,7 +15840,7 @@
       </c>
       <c r="S145" s="3"/>
       <c r="T145" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U145" s="3" t="s">
         <v>39</v>
@@ -15922,7 +15919,7 @@
       </c>
       <c r="S146" s="3"/>
       <c r="T146" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U146" s="3" t="s">
         <v>39</v>
@@ -16001,7 +15998,7 @@
       </c>
       <c r="S147" s="3"/>
       <c r="T147" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U147" s="3" t="s">
         <v>39</v>
@@ -16080,7 +16077,7 @@
       </c>
       <c r="S148" s="3"/>
       <c r="T148" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U148" s="3" t="s">
         <v>39</v>
@@ -16159,7 +16156,7 @@
       </c>
       <c r="S149" s="3"/>
       <c r="T149" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U149" s="3" t="s">
         <v>39</v>
@@ -16238,7 +16235,7 @@
       </c>
       <c r="S150" s="3"/>
       <c r="T150" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U150" s="3" t="s">
         <v>39</v>
@@ -16317,7 +16314,7 @@
       </c>
       <c r="S151" s="3"/>
       <c r="T151" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U151" s="3" t="s">
         <v>39</v>
@@ -16396,7 +16393,7 @@
       </c>
       <c r="S152" s="3"/>
       <c r="T152" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U152" s="3" t="s">
         <v>39</v>
@@ -16475,7 +16472,7 @@
       </c>
       <c r="S153" s="3"/>
       <c r="T153" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U153" s="3" t="s">
         <v>39</v>
@@ -16554,7 +16551,7 @@
       </c>
       <c r="S154" s="3"/>
       <c r="T154" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U154" s="3" t="s">
         <v>39</v>
@@ -16633,7 +16630,7 @@
       </c>
       <c r="S155" s="3"/>
       <c r="T155" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U155" s="3" t="s">
         <v>39</v>
@@ -16712,7 +16709,7 @@
       </c>
       <c r="S156" s="3"/>
       <c r="T156" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U156" s="3" t="s">
         <v>39</v>
@@ -16791,7 +16788,7 @@
       </c>
       <c r="S157" s="3"/>
       <c r="T157" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U157" s="3" t="s">
         <v>39</v>
@@ -16870,7 +16867,7 @@
       </c>
       <c r="S158" s="3"/>
       <c r="T158" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U158" s="3" t="s">
         <v>39</v>
@@ -17219,7 +17216,7 @@
         <v>845</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>29</v>
@@ -17269,7 +17266,7 @@
       </c>
       <c r="S163" s="3"/>
       <c r="T163" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U163" s="3" t="s">
         <v>39</v>
@@ -17298,7 +17295,7 @@
         <v>852</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>29</v>
@@ -17348,7 +17345,7 @@
       </c>
       <c r="S164" s="3"/>
       <c r="T164" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U164" s="3" t="s">
         <v>39</v>
@@ -17377,7 +17374,7 @@
         <v>855</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>29</v>
@@ -17427,7 +17424,7 @@
       </c>
       <c r="S165" s="3"/>
       <c r="T165" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U165" s="3" t="s">
         <v>39</v>
@@ -17456,7 +17453,7 @@
         <v>858</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>29</v>
@@ -17506,7 +17503,7 @@
       </c>
       <c r="S166" s="3"/>
       <c r="T166" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U166" s="3" t="s">
         <v>39</v>
@@ -17535,7 +17532,7 @@
         <v>861</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>29</v>
@@ -17585,7 +17582,7 @@
       </c>
       <c r="S167" s="3"/>
       <c r="T167" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U167" s="3" t="s">
         <v>39</v>
@@ -17614,7 +17611,7 @@
         <v>864</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>29</v>
@@ -17664,7 +17661,7 @@
       </c>
       <c r="S168" s="3"/>
       <c r="T168" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U168" s="3" t="s">
         <v>39</v>
@@ -17693,7 +17690,7 @@
         <v>867</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>29</v>
@@ -17743,7 +17740,7 @@
       </c>
       <c r="S169" s="3"/>
       <c r="T169" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U169" s="3" t="s">
         <v>39</v>
@@ -17772,7 +17769,7 @@
         <v>870</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>29</v>
@@ -17822,7 +17819,7 @@
       </c>
       <c r="S170" s="3"/>
       <c r="T170" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U170" s="3" t="s">
         <v>39</v>
@@ -17851,7 +17848,7 @@
         <v>873</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>29</v>
@@ -17901,7 +17898,7 @@
       </c>
       <c r="S171" s="3"/>
       <c r="T171" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U171" s="3" t="s">
         <v>39</v>
@@ -17930,7 +17927,7 @@
         <v>876</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>29</v>
@@ -17980,7 +17977,7 @@
       </c>
       <c r="S172" s="3"/>
       <c r="T172" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U172" s="3" t="s">
         <v>39</v>
@@ -18009,7 +18006,7 @@
         <v>879</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>29</v>
@@ -18059,7 +18056,7 @@
       </c>
       <c r="S173" s="3"/>
       <c r="T173" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U173" s="3" t="s">
         <v>39</v>
@@ -18088,7 +18085,7 @@
         <v>882</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>29</v>
@@ -18138,7 +18135,7 @@
       </c>
       <c r="S174" s="3"/>
       <c r="T174" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U174" s="3" t="s">
         <v>39</v>
@@ -18167,7 +18164,7 @@
         <v>885</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>29</v>
@@ -18217,7 +18214,7 @@
       </c>
       <c r="S175" s="3"/>
       <c r="T175" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U175" s="3" t="s">
         <v>39</v>
@@ -18246,7 +18243,7 @@
         <v>888</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>29</v>
@@ -18296,7 +18293,7 @@
       </c>
       <c r="S176" s="3"/>
       <c r="T176" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U176" s="3" t="s">
         <v>39</v>
@@ -18325,7 +18322,7 @@
         <v>891</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>29</v>
@@ -18375,7 +18372,7 @@
       </c>
       <c r="S177" s="3"/>
       <c r="T177" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U177" s="3" t="s">
         <v>39</v>
@@ -18404,7 +18401,7 @@
         <v>894</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>29</v>
@@ -18454,7 +18451,7 @@
       </c>
       <c r="S178" s="3"/>
       <c r="T178" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U178" s="3" t="s">
         <v>39</v>
@@ -18483,7 +18480,7 @@
         <v>897</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>29</v>
@@ -18533,7 +18530,7 @@
       </c>
       <c r="S179" s="3"/>
       <c r="T179" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U179" s="3" t="s">
         <v>39</v>
@@ -18562,7 +18559,7 @@
         <v>900</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>29</v>
@@ -18612,7 +18609,7 @@
       </c>
       <c r="S180" s="3"/>
       <c r="T180" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U180" s="3" t="s">
         <v>39</v>
@@ -18641,7 +18638,7 @@
         <v>903</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>29</v>
@@ -18691,7 +18688,7 @@
       </c>
       <c r="S181" s="3"/>
       <c r="T181" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U181" s="3" t="s">
         <v>39</v>
@@ -18720,7 +18717,7 @@
         <v>906</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>29</v>
@@ -18770,7 +18767,7 @@
       </c>
       <c r="S182" s="3"/>
       <c r="T182" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U182" s="3" t="s">
         <v>39</v>
@@ -18799,7 +18796,7 @@
         <v>909</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>29</v>
@@ -18849,7 +18846,7 @@
       </c>
       <c r="S183" s="3"/>
       <c r="T183" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U183" s="3" t="s">
         <v>39</v>
@@ -18878,7 +18875,7 @@
         <v>912</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>29</v>
@@ -18928,7 +18925,7 @@
       </c>
       <c r="S184" s="3"/>
       <c r="T184" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U184" s="3" t="s">
         <v>39</v>
@@ -18957,7 +18954,7 @@
         <v>915</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>29</v>
@@ -19007,7 +19004,7 @@
       </c>
       <c r="S185" s="3"/>
       <c r="T185" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U185" s="3" t="s">
         <v>39</v>
@@ -19036,7 +19033,7 @@
         <v>918</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>29</v>
@@ -19086,7 +19083,7 @@
       </c>
       <c r="S186" s="3"/>
       <c r="T186" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U186" s="3" t="s">
         <v>39</v>
@@ -19115,7 +19112,7 @@
         <v>921</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>29</v>
@@ -19165,7 +19162,7 @@
       </c>
       <c r="S187" s="3"/>
       <c r="T187" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U187" s="3" t="s">
         <v>39</v>
@@ -19194,7 +19191,7 @@
         <v>924</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>29</v>
@@ -19244,7 +19241,7 @@
       </c>
       <c r="S188" s="3"/>
       <c r="T188" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U188" s="3" t="s">
         <v>39</v>
@@ -19273,7 +19270,7 @@
         <v>927</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>29</v>
@@ -19323,7 +19320,7 @@
       </c>
       <c r="S189" s="3"/>
       <c r="T189" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U189" s="3" t="s">
         <v>39</v>
@@ -19352,7 +19349,7 @@
         <v>930</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>29</v>
@@ -19402,7 +19399,7 @@
       </c>
       <c r="S190" s="3"/>
       <c r="T190" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U190" s="3" t="s">
         <v>39</v>
@@ -19431,7 +19428,7 @@
         <v>933</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>29</v>
@@ -19481,7 +19478,7 @@
       </c>
       <c r="S191" s="3"/>
       <c r="T191" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U191" s="3" t="s">
         <v>39</v>
@@ -19510,7 +19507,7 @@
         <v>936</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>29</v>
@@ -19560,7 +19557,7 @@
       </c>
       <c r="S192" s="3"/>
       <c r="T192" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U192" s="3" t="s">
         <v>39</v>
@@ -19589,7 +19586,7 @@
         <v>939</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>29</v>
@@ -19639,7 +19636,7 @@
       </c>
       <c r="S193" s="3"/>
       <c r="T193" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U193" s="3" t="s">
         <v>39</v>
@@ -19668,7 +19665,7 @@
         <v>942</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>29</v>
@@ -19718,7 +19715,7 @@
       </c>
       <c r="S194" s="3"/>
       <c r="T194" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U194" s="3" t="s">
         <v>39</v>
@@ -19747,7 +19744,7 @@
         <v>945</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>29</v>
@@ -19797,7 +19794,7 @@
       </c>
       <c r="S195" s="3"/>
       <c r="T195" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U195" s="3" t="s">
         <v>39</v>
@@ -19826,7 +19823,7 @@
         <v>948</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>29</v>
@@ -19876,7 +19873,7 @@
       </c>
       <c r="S196" s="3"/>
       <c r="T196" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U196" s="3" t="s">
         <v>39</v>
@@ -19955,7 +19952,7 @@
       </c>
       <c r="S197" s="3"/>
       <c r="T197" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U197" s="3" t="s">
         <v>39</v>
@@ -20034,7 +20031,7 @@
       </c>
       <c r="S198" s="3"/>
       <c r="T198" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U198" s="3" t="s">
         <v>39</v>
@@ -20113,7 +20110,7 @@
       </c>
       <c r="S199" s="3"/>
       <c r="T199" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U199" s="3" t="s">
         <v>39</v>
@@ -20192,7 +20189,7 @@
       </c>
       <c r="S200" s="3"/>
       <c r="T200" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U200" s="3" t="s">
         <v>39</v>
@@ -20271,7 +20268,7 @@
       </c>
       <c r="S201" s="3"/>
       <c r="T201" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U201" s="3" t="s">
         <v>39</v>
@@ -20350,7 +20347,7 @@
       </c>
       <c r="S202" s="3"/>
       <c r="T202" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U202" s="3" t="s">
         <v>39</v>
@@ -20461,7 +20458,7 @@
         <v>28</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>164</v>
@@ -20470,7 +20467,7 @@
         <v>168</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>968</v>
@@ -20497,10 +20494,10 @@
         <v>44147</v>
       </c>
       <c r="O204" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P204" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q204" s="3"/>
       <c r="R204" s="3" t="s">
@@ -20508,7 +20505,7 @@
       </c>
       <c r="S204" s="3"/>
       <c r="T204" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U204" s="3" t="s">
         <v>39</v>
@@ -20576,10 +20573,10 @@
         <v>44280</v>
       </c>
       <c r="O205" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P205" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q205" s="4">
         <v>45239</v>
@@ -20589,7 +20586,7 @@
       </c>
       <c r="S205" s="3"/>
       <c r="T205" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U205" s="3" t="s">
         <v>39</v>
@@ -20657,10 +20654,10 @@
         <v>44280</v>
       </c>
       <c r="O206" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P206" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q206" s="4">
         <v>45239</v>
@@ -20670,7 +20667,7 @@
       </c>
       <c r="S206" s="3"/>
       <c r="T206" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U206" s="3" t="s">
         <v>39</v>
@@ -20790,7 +20787,7 @@
         <v>31</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>994</v>
@@ -20817,10 +20814,10 @@
         <v>1000</v>
       </c>
       <c r="O208" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P208" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q208" s="3"/>
       <c r="R208" s="3" t="s">
@@ -20960,7 +20957,7 @@
         <v>1015</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K210" s="3" t="s">
         <v>1016</v>
@@ -20986,7 +20983,7 @@
       </c>
       <c r="S210" s="3"/>
       <c r="T210" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U210" s="3" t="s">
         <v>39</v>
@@ -21039,7 +21036,7 @@
         <v>1015</v>
       </c>
       <c r="J211" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K211" s="3" t="s">
         <v>1016</v>
@@ -21065,7 +21062,7 @@
       </c>
       <c r="S211" s="3"/>
       <c r="T211" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U211" s="3" t="s">
         <v>39</v>
@@ -21133,7 +21130,7 @@
         <v>44518</v>
       </c>
       <c r="O212" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P212" s="4">
         <v>44896</v>
@@ -21212,7 +21209,7 @@
         <v>44518</v>
       </c>
       <c r="O213" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P213" s="4">
         <v>44896</v>
@@ -21291,10 +21288,10 @@
         <v>44531</v>
       </c>
       <c r="O214" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P214" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q214" s="4">
         <v>44735</v>
@@ -21303,7 +21300,7 @@
         <v>39</v>
       </c>
       <c r="S214" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="T214" s="3" t="s">
         <v>332</v>
@@ -21374,10 +21371,10 @@
         <v>44531</v>
       </c>
       <c r="O215" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P215" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q215" s="4">
         <v>44735</v>
@@ -21386,7 +21383,7 @@
         <v>39</v>
       </c>
       <c r="S215" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="T215" s="3" t="s">
         <v>332</v>
@@ -21457,10 +21454,10 @@
         <v>44013</v>
       </c>
       <c r="O216" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P216" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q216" s="3"/>
       <c r="R216" s="3" t="s">
@@ -21536,10 +21533,10 @@
         <v>44013</v>
       </c>
       <c r="O217" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P217" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q217" s="3"/>
       <c r="R217" s="3" t="s">
@@ -21600,7 +21597,7 @@
         <v>34</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K218" s="3" t="s">
         <v>1062</v>
@@ -21613,7 +21610,7 @@
       </c>
       <c r="N218" s="3"/>
       <c r="O218" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P218" s="4">
         <v>44896</v>
@@ -21624,7 +21621,7 @@
       </c>
       <c r="S218" s="3"/>
       <c r="T218" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U218" s="3" t="s">
         <v>39</v>
@@ -21677,7 +21674,7 @@
         <v>34</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K219" s="3" t="s">
         <v>1062</v>
@@ -21690,7 +21687,7 @@
       </c>
       <c r="N219" s="3"/>
       <c r="O219" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P219" s="4">
         <v>44896</v>
@@ -21701,7 +21698,7 @@
       </c>
       <c r="S219" s="3"/>
       <c r="T219" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U219" s="3" t="s">
         <v>39</v>
@@ -21769,10 +21766,10 @@
         <v>44951</v>
       </c>
       <c r="O220" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P220" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q220" s="4">
         <v>45428</v>
@@ -21781,7 +21778,7 @@
         <v>39</v>
       </c>
       <c r="S220" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="T220" s="3" t="s">
         <v>61</v>
@@ -21852,19 +21849,19 @@
         <v>44951</v>
       </c>
       <c r="O221" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P221" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q221" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="R221" s="3" t="s">
         <v>39</v>
       </c>
       <c r="S221" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="T221" s="3" t="s">
         <v>61</v>
@@ -21920,7 +21917,7 @@
         <v>34</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K222" s="3" t="s">
         <v>1093</v>
@@ -21938,7 +21935,7 @@
         <v>45239</v>
       </c>
       <c r="P222" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q222" s="3"/>
       <c r="R222" s="3" t="s">
@@ -21999,7 +21996,7 @@
         <v>34</v>
       </c>
       <c r="J223" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K223" s="3" t="s">
         <v>1093</v>
@@ -22017,7 +22014,7 @@
         <v>45239</v>
       </c>
       <c r="P223" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q223" s="3"/>
       <c r="R223" s="3" t="s">
@@ -22054,7 +22051,7 @@
         <v>1101</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>29</v>
@@ -22137,13 +22134,13 @@
         <v>451</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E225" s="3" t="s">
         <v>452</v>
@@ -22200,7 +22197,7 @@
         <v>39</v>
       </c>
       <c r="W225" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X225" s="3" t="s">
         <v>39</v>
@@ -22257,10 +22254,10 @@
         <v>44951</v>
       </c>
       <c r="O226" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P226" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q226" s="3"/>
       <c r="R226" s="3" t="s">
@@ -22268,7 +22265,7 @@
       </c>
       <c r="S226" s="3"/>
       <c r="T226" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U226" s="3" t="s">
         <v>39</v>
@@ -22336,10 +22333,10 @@
         <v>44951</v>
       </c>
       <c r="O227" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P227" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q227" s="3"/>
       <c r="R227" s="3" t="s">
@@ -22347,7 +22344,7 @@
       </c>
       <c r="S227" s="3"/>
       <c r="T227" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U227" s="3" t="s">
         <v>39</v>
@@ -22428,7 +22425,7 @@
       </c>
       <c r="S228" s="3"/>
       <c r="T228" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U228" s="3" t="s">
         <v>39</v>
@@ -22509,7 +22506,7 @@
       </c>
       <c r="S229" s="3"/>
       <c r="T229" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U229" s="3" t="s">
         <v>39</v>
@@ -22538,7 +22535,7 @@
         <v>1131</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>29</v>
@@ -22562,7 +22559,7 @@
         <v>34</v>
       </c>
       <c r="J230" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K230" s="3" t="s">
         <v>1134</v>
@@ -22588,7 +22585,7 @@
       </c>
       <c r="S230" s="3"/>
       <c r="T230" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U230" s="3" t="s">
         <v>39</v>
@@ -22641,7 +22638,7 @@
         <v>34</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K231" s="3" t="s">
         <v>1134</v>
@@ -22667,7 +22664,7 @@
       </c>
       <c r="S231" s="3"/>
       <c r="T231" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U231" s="3" t="s">
         <v>39</v>
@@ -22908,7 +22905,7 @@
         <v>45602</v>
       </c>
       <c r="T234" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U234" s="3" t="s">
         <v>39</v>
@@ -22991,7 +22988,7 @@
         <v>45602</v>
       </c>
       <c r="T235" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U235" s="3" t="s">
         <v>39</v>
@@ -23070,7 +23067,7 @@
       </c>
       <c r="S236" s="3"/>
       <c r="T236" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="U236" s="3" t="s">
         <v>39</v>
@@ -23149,7 +23146,7 @@
       </c>
       <c r="S237" s="3"/>
       <c r="T237" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="U237" s="3" t="s">
         <v>39</v>
@@ -23228,7 +23225,7 @@
       </c>
       <c r="S238" s="3"/>
       <c r="T238" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="U238" s="3" t="s">
         <v>39</v>
@@ -23309,7 +23306,7 @@
       </c>
       <c r="S239" s="3"/>
       <c r="T239" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="U239" s="3" t="s">
         <v>39</v>
@@ -23347,50 +23344,48 @@
         <v>30</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>31</v>
+        <v>1195</v>
       </c>
       <c r="F240" s="4">
-        <v>45370</v>
+        <v>45078</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>1185</v>
+        <v>1196</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>1187</v>
+        <v>1197</v>
       </c>
       <c r="I240" s="3" t="s">
-        <v>1186</v>
+        <v>1198</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>1188</v>
+        <v>39</v>
       </c>
       <c r="K240" s="3" t="s">
-        <v>1189</v>
+        <v>1199</v>
       </c>
       <c r="L240" s="3" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="M240" s="3" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="N240" s="4">
-        <v>45279</v>
+        <v>44851</v>
       </c>
       <c r="O240" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P240" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q240" s="4">
-        <v>45461</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="Q240" s="3"/>
       <c r="R240" s="3" t="s">
         <v>39</v>
       </c>
       <c r="S240" s="3"/>
       <c r="T240" s="3" t="s">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="U240" s="3" t="s">
         <v>39</v>
@@ -23399,7 +23394,7 @@
         <v>39</v>
       </c>
       <c r="W240" s="3" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="X240" s="3" t="s">
         <v>39</v>
@@ -23408,7 +23403,7 @@
         <v>39</v>
       </c>
       <c r="Z240" s="3" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="AA240" s="3" t="s">
         <v>39</v>
@@ -23416,10 +23411,10 @@
     </row>
     <row r="241" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>29</v>
@@ -23428,40 +23423,40 @@
         <v>30</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F241" s="4">
         <v>45078</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="H241" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I241" s="3" t="s">
         <v>1198</v>
       </c>
-      <c r="I241" s="3" t="s">
+      <c r="J241" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K241" s="3" t="s">
         <v>1199</v>
       </c>
-      <c r="J241" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K241" s="3" t="s">
-        <v>1200</v>
-      </c>
       <c r="L241" s="3" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="M241" s="3" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="N241" s="4">
         <v>44851</v>
       </c>
       <c r="O241" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P241" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q241" s="3"/>
       <c r="R241" s="3" t="s">
@@ -23478,16 +23473,16 @@
         <v>39</v>
       </c>
       <c r="W241" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="X241" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y241" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z241" s="3" t="s">
         <v>1201</v>
-      </c>
-      <c r="X241" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y241" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z241" s="3" t="s">
-        <v>1202</v>
       </c>
       <c r="AA241" s="3" t="s">
         <v>39</v>
@@ -23495,10 +23490,10 @@
     </row>
     <row r="242" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>29</v>
@@ -23507,40 +23502,40 @@
         <v>30</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F242" s="4">
         <v>45078</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="I242" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J242" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K242" s="3" t="s">
         <v>1199</v>
       </c>
-      <c r="J242" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K242" s="3" t="s">
-        <v>1200</v>
-      </c>
       <c r="L242" s="3" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="M242" s="3" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="N242" s="4">
         <v>44851</v>
       </c>
       <c r="O242" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P242" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q242" s="3"/>
       <c r="R242" s="3" t="s">
@@ -23557,16 +23552,16 @@
         <v>39</v>
       </c>
       <c r="W242" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="X242" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y242" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z242" s="3" t="s">
         <v>1201</v>
-      </c>
-      <c r="X242" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y242" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z242" s="3" t="s">
-        <v>1202</v>
       </c>
       <c r="AA242" s="3" t="s">
         <v>39</v>
@@ -23574,60 +23569,64 @@
     </row>
     <row r="243" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>1196</v>
+        <v>1083</v>
       </c>
       <c r="F243" s="4">
-        <v>45078</v>
+        <v>45390</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="I243" s="3" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>39</v>
+        <v>1086</v>
       </c>
       <c r="K243" s="3" t="s">
-        <v>1200</v>
+        <v>1087</v>
       </c>
       <c r="L243" s="3" t="s">
-        <v>1199</v>
+        <v>1088</v>
       </c>
       <c r="M243" s="3" t="s">
-        <v>1199</v>
+        <v>1089</v>
       </c>
       <c r="N243" s="4">
-        <v>44851</v>
-      </c>
-      <c r="O243" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P243" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q243" s="3"/>
+        <v>45372</v>
+      </c>
+      <c r="O243" s="4">
+        <v>45603</v>
+      </c>
+      <c r="P243" s="4">
+        <v>45631</v>
+      </c>
+      <c r="Q243" s="4">
+        <v>45428</v>
+      </c>
       <c r="R243" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="S243" s="3"/>
+      <c r="S243" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="T243" s="3" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="U243" s="3" t="s">
         <v>39</v>
@@ -23636,7 +23635,7 @@
         <v>39</v>
       </c>
       <c r="W243" s="3" t="s">
-        <v>1201</v>
+        <v>1090</v>
       </c>
       <c r="X243" s="3" t="s">
         <v>39</v>
@@ -23645,7 +23644,7 @@
         <v>39</v>
       </c>
       <c r="Z243" s="3" t="s">
-        <v>1202</v>
+        <v>1081</v>
       </c>
       <c r="AA243" s="3" t="s">
         <v>39</v>
@@ -23653,7 +23652,7 @@
     </row>
     <row r="244" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>28</v>
@@ -23662,55 +23661,51 @@
         <v>29</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>1083</v>
+        <v>1195</v>
       </c>
       <c r="F244" s="4">
-        <v>45390</v>
+        <v>45078</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="I244" s="3" t="s">
-        <v>1212</v>
+        <v>1198</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>1086</v>
+        <v>39</v>
       </c>
       <c r="K244" s="3" t="s">
-        <v>1087</v>
+        <v>1199</v>
       </c>
       <c r="L244" s="3" t="s">
-        <v>1088</v>
+        <v>1198</v>
       </c>
       <c r="M244" s="3" t="s">
-        <v>1089</v>
+        <v>1198</v>
       </c>
       <c r="N244" s="4">
-        <v>45372</v>
-      </c>
-      <c r="O244" s="4">
-        <v>45603</v>
-      </c>
-      <c r="P244" s="4">
-        <v>45631</v>
-      </c>
-      <c r="Q244" s="4">
-        <v>45428</v>
-      </c>
+        <v>44851</v>
+      </c>
+      <c r="O244" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P244" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q244" s="3"/>
       <c r="R244" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="S244" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="S244" s="3"/>
       <c r="T244" s="3" t="s">
-        <v>61</v>
+        <v>197</v>
       </c>
       <c r="U244" s="3" t="s">
         <v>39</v>
@@ -23719,7 +23714,7 @@
         <v>39</v>
       </c>
       <c r="W244" s="3" t="s">
-        <v>1090</v>
+        <v>1200</v>
       </c>
       <c r="X244" s="3" t="s">
         <v>39</v>
@@ -23728,7 +23723,7 @@
         <v>39</v>
       </c>
       <c r="Z244" s="3" t="s">
-        <v>1081</v>
+        <v>1201</v>
       </c>
       <c r="AA244" s="3" t="s">
         <v>39</v>
@@ -23736,7 +23731,7 @@
     </row>
     <row r="245" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>28</v>
@@ -23748,40 +23743,40 @@
         <v>30</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F245" s="4">
         <v>45078</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="I245" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="J245" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K245" s="3" t="s">
         <v>1199</v>
       </c>
-      <c r="J245" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K245" s="3" t="s">
-        <v>1200</v>
-      </c>
       <c r="L245" s="3" t="s">
-        <v>1199</v>
+        <v>1219</v>
       </c>
       <c r="M245" s="3" t="s">
-        <v>1199</v>
+        <v>1220</v>
       </c>
       <c r="N245" s="4">
         <v>44851</v>
       </c>
       <c r="O245" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P245" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q245" s="3"/>
       <c r="R245" s="3" t="s">
@@ -23789,7 +23784,7 @@
       </c>
       <c r="S245" s="3"/>
       <c r="T245" s="3" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="U245" s="3" t="s">
         <v>39</v>
@@ -23798,16 +23793,16 @@
         <v>39</v>
       </c>
       <c r="W245" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="X245" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y245" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z245" s="3" t="s">
         <v>1201</v>
-      </c>
-      <c r="X245" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y245" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z245" s="3" t="s">
-        <v>1202</v>
       </c>
       <c r="AA245" s="3" t="s">
         <v>39</v>
@@ -23815,10 +23810,10 @@
     </row>
     <row r="246" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>29</v>
@@ -23827,40 +23822,40 @@
         <v>30</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F246" s="4">
         <v>45078</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="H246" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I246" s="3" t="s">
         <v>1218</v>
       </c>
-      <c r="I246" s="3" t="s">
+      <c r="J246" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K246" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="L246" s="3" t="s">
         <v>1219</v>
       </c>
-      <c r="J246" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K246" s="3" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L246" s="3" t="s">
+      <c r="M246" s="3" t="s">
         <v>1220</v>
-      </c>
-      <c r="M246" s="3" t="s">
-        <v>1221</v>
       </c>
       <c r="N246" s="4">
         <v>44851</v>
       </c>
       <c r="O246" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P246" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q246" s="3"/>
       <c r="R246" s="3" t="s">
@@ -23868,7 +23863,7 @@
       </c>
       <c r="S246" s="3"/>
       <c r="T246" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U246" s="3" t="s">
         <v>39</v>
@@ -23877,16 +23872,16 @@
         <v>39</v>
       </c>
       <c r="W246" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="X246" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y246" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z246" s="3" t="s">
         <v>1201</v>
-      </c>
-      <c r="X246" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y246" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z246" s="3" t="s">
-        <v>1202</v>
       </c>
       <c r="AA246" s="3" t="s">
         <v>39</v>
@@ -23894,60 +23889,64 @@
     </row>
     <row r="247" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>1196</v>
+        <v>31</v>
       </c>
       <c r="F247" s="4">
-        <v>45078</v>
+        <v>45412</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="I247" s="3" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="J247" s="3" t="s">
-        <v>39</v>
+        <v>1228</v>
       </c>
       <c r="K247" s="3" t="s">
-        <v>1200</v>
+        <v>1229</v>
       </c>
       <c r="L247" s="3" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="M247" s="3" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="N247" s="4">
-        <v>44851</v>
-      </c>
-      <c r="O247" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P247" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q247" s="3"/>
-      <c r="R247" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S247" s="3"/>
+        <v>45372</v>
+      </c>
+      <c r="O247" s="4">
+        <v>45666</v>
+      </c>
+      <c r="P247" s="4">
+        <v>45694</v>
+      </c>
+      <c r="Q247" s="4">
+        <v>45534</v>
+      </c>
+      <c r="R247" s="4">
+        <v>45644</v>
+      </c>
+      <c r="S247" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="T247" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U247" s="3" t="s">
         <v>39</v>
@@ -23956,7 +23955,7 @@
         <v>39</v>
       </c>
       <c r="W247" s="3" t="s">
-        <v>1201</v>
+        <v>1232</v>
       </c>
       <c r="X247" s="3" t="s">
         <v>39</v>
@@ -23965,7 +23964,7 @@
         <v>39</v>
       </c>
       <c r="Z247" s="3" t="s">
-        <v>1202</v>
+        <v>1233</v>
       </c>
       <c r="AA247" s="3" t="s">
         <v>39</v>
@@ -23973,10 +23972,10 @@
     </row>
     <row r="248" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>1225</v>
+        <v>1234</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>29</v>
@@ -23991,25 +23990,25 @@
         <v>45412</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>1226</v>
+        <v>1235</v>
       </c>
       <c r="H248" s="3" t="s">
         <v>1227</v>
       </c>
       <c r="I248" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J248" s="3" t="s">
         <v>1228</v>
       </c>
-      <c r="J248" s="3" t="s">
+      <c r="K248" s="3" t="s">
         <v>1229</v>
       </c>
-      <c r="K248" s="3" t="s">
+      <c r="L248" s="3" t="s">
         <v>1230</v>
       </c>
-      <c r="L248" s="3" t="s">
+      <c r="M248" s="3" t="s">
         <v>1231</v>
-      </c>
-      <c r="M248" s="3" t="s">
-        <v>1232</v>
       </c>
       <c r="N248" s="4">
         <v>45372</v>
@@ -24023,14 +24022,14 @@
       <c r="Q248" s="4">
         <v>45534</v>
       </c>
-      <c r="R248" s="4">
+      <c r="R248" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S248" s="4">
         <v>45644</v>
       </c>
-      <c r="S248" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="T248" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U248" s="3" t="s">
         <v>39</v>
@@ -24039,16 +24038,16 @@
         <v>39</v>
       </c>
       <c r="W248" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="X248" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y248" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z248" s="3" t="s">
         <v>1233</v>
-      </c>
-      <c r="X248" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y248" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z248" s="3" t="s">
-        <v>1234</v>
       </c>
       <c r="AA248" s="3" t="s">
         <v>39</v>
@@ -24056,64 +24055,60 @@
     </row>
     <row r="249" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>42</v>
+        <v>164</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F249" s="4">
-        <v>45412</v>
+        <v>45503</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H249" s="3" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="I249" s="3" t="s">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="J249" s="3" t="s">
-        <v>1229</v>
+        <v>1240</v>
       </c>
       <c r="K249" s="3" t="s">
-        <v>1230</v>
+        <v>1241</v>
       </c>
       <c r="L249" s="3" t="s">
-        <v>1231</v>
+        <v>1242</v>
       </c>
       <c r="M249" s="3" t="s">
-        <v>1232</v>
+        <v>1243</v>
       </c>
       <c r="N249" s="4">
-        <v>45372</v>
-      </c>
-      <c r="O249" s="4">
-        <v>45666</v>
-      </c>
-      <c r="P249" s="4">
-        <v>45694</v>
-      </c>
-      <c r="Q249" s="4">
-        <v>45534</v>
-      </c>
+        <v>45169</v>
+      </c>
+      <c r="O249" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P249" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q249" s="3"/>
       <c r="R249" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="S249" s="4">
-        <v>45644</v>
-      </c>
+      <c r="S249" s="3"/>
       <c r="T249" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="U249" s="3" t="s">
         <v>39</v>
@@ -24122,7 +24117,7 @@
         <v>39</v>
       </c>
       <c r="W249" s="3" t="s">
-        <v>1233</v>
+        <v>1244</v>
       </c>
       <c r="X249" s="3" t="s">
         <v>39</v>
@@ -24131,7 +24126,7 @@
         <v>39</v>
       </c>
       <c r="Z249" s="3" t="s">
-        <v>1234</v>
+        <v>39</v>
       </c>
       <c r="AA249" s="3" t="s">
         <v>39</v>
@@ -24139,10 +24134,10 @@
     </row>
     <row r="250" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>29</v>
@@ -24157,34 +24152,34 @@
         <v>45503</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H250" s="3" t="s">
         <v>1239</v>
       </c>
       <c r="I250" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J250" s="3" t="s">
         <v>1240</v>
       </c>
-      <c r="J250" s="3" t="s">
+      <c r="K250" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="K250" s="3" t="s">
+      <c r="L250" s="3" t="s">
         <v>1242</v>
       </c>
-      <c r="L250" s="3" t="s">
+      <c r="M250" s="3" t="s">
         <v>1243</v>
-      </c>
-      <c r="M250" s="3" t="s">
-        <v>1244</v>
       </c>
       <c r="N250" s="4">
         <v>45169</v>
       </c>
       <c r="O250" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="P250" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="Q250" s="3"/>
       <c r="R250" s="3" t="s">
@@ -24192,7 +24187,7 @@
       </c>
       <c r="S250" s="3"/>
       <c r="T250" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U250" s="3" t="s">
         <v>39</v>
@@ -24201,7 +24196,7 @@
         <v>39</v>
       </c>
       <c r="W250" s="3" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="X250" s="3" t="s">
         <v>39</v>
@@ -24221,66 +24216,70 @@
         <v>1246</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>164</v>
+        <v>42</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F251" s="4">
-        <v>45503</v>
+        <v>45839</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>1238</v>
+        <v>1247</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="I251" s="3" t="s">
-        <v>1240</v>
+        <v>1249</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1241</v>
+        <v>1250</v>
       </c>
       <c r="K251" s="3" t="s">
-        <v>1242</v>
+        <v>1251</v>
       </c>
       <c r="L251" s="3" t="s">
-        <v>1243</v>
+        <v>1252</v>
       </c>
       <c r="M251" s="3" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="N251" s="4">
-        <v>45169</v>
+        <v>45666</v>
       </c>
       <c r="O251" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P251" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q251" s="3"/>
-      <c r="R251" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S251" s="3"/>
+        <v>1254</v>
+      </c>
+      <c r="P251" s="4">
+        <v>45973</v>
+      </c>
+      <c r="Q251" s="4">
+        <v>45860</v>
+      </c>
+      <c r="R251" s="4">
+        <v>45952</v>
+      </c>
+      <c r="S251" s="4">
+        <v>46029</v>
+      </c>
       <c r="T251" s="3" t="s">
-        <v>127</v>
+        <v>332</v>
       </c>
       <c r="U251" s="3" t="s">
         <v>39</v>
       </c>
       <c r="V251" s="3" t="s">
-        <v>39</v>
+        <v>1255</v>
       </c>
       <c r="W251" s="3" t="s">
-        <v>1245</v>
+        <v>1256</v>
       </c>
       <c r="X251" s="3" t="s">
         <v>39</v>
@@ -24297,10 +24296,10 @@
     </row>
     <row r="252" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>29</v>
@@ -24315,31 +24314,31 @@
         <v>45839</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H252" s="3" t="s">
         <v>1249</v>
       </c>
       <c r="I252" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="J252" s="3" t="s">
         <v>1250</v>
       </c>
-      <c r="J252" s="3" t="s">
-        <v>1251</v>
-      </c>
       <c r="K252" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="L252" s="3" t="s">
         <v>1252</v>
       </c>
-      <c r="L252" s="3" t="s">
+      <c r="M252" s="3" t="s">
         <v>1253</v>
-      </c>
-      <c r="M252" s="3" t="s">
-        <v>1254</v>
       </c>
       <c r="N252" s="4">
         <v>45666</v>
       </c>
       <c r="O252" s="3" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="P252" s="4">
         <v>45973</v>
@@ -24360,10 +24359,10 @@
         <v>39</v>
       </c>
       <c r="V252" s="3" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="W252" s="3" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="X252" s="3" t="s">
         <v>39</v>
@@ -24380,10 +24379,10 @@
     </row>
     <row r="253" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>29</v>
@@ -24395,58 +24394,56 @@
         <v>31</v>
       </c>
       <c r="F253" s="4">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>1248</v>
+        <v>1261</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>1250</v>
+        <v>1262</v>
       </c>
       <c r="I253" s="3" t="s">
-        <v>1249</v>
+        <v>34</v>
       </c>
       <c r="J253" s="3" t="s">
-        <v>1251</v>
+        <v>1263</v>
       </c>
       <c r="K253" s="3" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="L253" s="3" t="s">
-        <v>1253</v>
+        <v>1265</v>
       </c>
       <c r="M253" s="3" t="s">
-        <v>1254</v>
+        <v>1266</v>
       </c>
       <c r="N253" s="4">
-        <v>45666</v>
-      </c>
-      <c r="O253" s="3" t="s">
-        <v>1255</v>
+        <v>45645</v>
+      </c>
+      <c r="O253" s="4">
+        <v>45974</v>
       </c>
       <c r="P253" s="4">
-        <v>45973</v>
+        <v>46002</v>
       </c>
       <c r="Q253" s="4">
-        <v>45860</v>
+        <v>45866</v>
       </c>
       <c r="R253" s="4">
-        <v>45952</v>
-      </c>
-      <c r="S253" s="4">
-        <v>46029</v>
-      </c>
+        <v>45958</v>
+      </c>
+      <c r="S253" s="3"/>
       <c r="T253" s="3" t="s">
-        <v>332</v>
+        <v>1267</v>
       </c>
       <c r="U253" s="3" t="s">
         <v>39</v>
       </c>
       <c r="V253" s="3" t="s">
-        <v>1256</v>
+        <v>1268</v>
       </c>
       <c r="W253" s="3" t="s">
-        <v>1260</v>
+        <v>1269</v>
       </c>
       <c r="X253" s="3" t="s">
         <v>39</v>
@@ -24463,10 +24460,10 @@
     </row>
     <row r="254" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>1261</v>
+        <v>1270</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>29</v>
@@ -24478,56 +24475,58 @@
         <v>31</v>
       </c>
       <c r="F254" s="4">
-        <v>45866</v>
+        <v>45812</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>1262</v>
+        <v>1271</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>1263</v>
+        <v>1272</v>
       </c>
       <c r="I254" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J254" s="3" t="s">
-        <v>1264</v>
+        <v>1273</v>
       </c>
       <c r="K254" s="3" t="s">
-        <v>1265</v>
+        <v>1274</v>
       </c>
       <c r="L254" s="3" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="M254" s="3" t="s">
-        <v>1267</v>
+        <v>1276</v>
       </c>
       <c r="N254" s="4">
-        <v>45645</v>
+        <v>45743</v>
       </c>
       <c r="O254" s="4">
-        <v>45974</v>
+        <v>46030</v>
       </c>
       <c r="P254" s="4">
-        <v>46002</v>
+        <v>46065</v>
       </c>
       <c r="Q254" s="4">
-        <v>45866</v>
+        <v>45867</v>
       </c>
       <c r="R254" s="4">
-        <v>45958</v>
-      </c>
-      <c r="S254" s="3"/>
+        <v>45961</v>
+      </c>
+      <c r="S254" s="3">
+        <v>0</v>
+      </c>
       <c r="T254" s="3" t="s">
-        <v>1268</v>
+        <v>126</v>
       </c>
       <c r="U254" s="3" t="s">
         <v>39</v>
       </c>
       <c r="V254" s="3" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="W254" s="3" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="X254" s="3" t="s">
         <v>39</v>
@@ -24544,10 +24543,10 @@
     </row>
     <row r="255" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>29</v>
@@ -24556,34 +24555,34 @@
         <v>42</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>31</v>
+        <v>1280</v>
       </c>
       <c r="F255" s="4">
-        <v>45812</v>
+        <v>45809</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>1272</v>
+        <v>1281</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>1273</v>
+        <v>1282</v>
       </c>
       <c r="I255" s="3" t="s">
-        <v>34</v>
+        <v>1283</v>
       </c>
       <c r="J255" s="3" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
       <c r="K255" s="3" t="s">
-        <v>1275</v>
+        <v>1285</v>
       </c>
       <c r="L255" s="3" t="s">
-        <v>1276</v>
+        <v>1286</v>
       </c>
       <c r="M255" s="3" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
       <c r="N255" s="4">
-        <v>45743</v>
+        <v>45666</v>
       </c>
       <c r="O255" s="4">
         <v>46030</v>
@@ -24592,25 +24591,25 @@
         <v>46065</v>
       </c>
       <c r="Q255" s="4">
-        <v>45867</v>
+        <v>45858</v>
       </c>
       <c r="R255" s="4">
-        <v>45961</v>
-      </c>
-      <c r="S255" s="3">
-        <v>0</v>
+        <v>45981</v>
+      </c>
+      <c r="S255" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="T255" s="3" t="s">
-        <v>127</v>
+        <v>1288</v>
       </c>
       <c r="U255" s="3" t="s">
         <v>39</v>
       </c>
       <c r="V255" s="3" t="s">
-        <v>1278</v>
+        <v>1289</v>
       </c>
       <c r="W255" s="3" t="s">
-        <v>1279</v>
+        <v>1290</v>
       </c>
       <c r="X255" s="3" t="s">
         <v>39</v>
@@ -24627,10 +24626,10 @@
     </row>
     <row r="256" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>1280</v>
+        <v>1291</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>29</v>
@@ -24639,31 +24638,31 @@
         <v>42</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F256" s="4">
         <v>45809</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>1283</v>
       </c>
       <c r="I256" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="J256" s="3" t="s">
         <v>1284</v>
       </c>
-      <c r="J256" s="3" t="s">
+      <c r="K256" s="3" t="s">
         <v>1285</v>
       </c>
-      <c r="K256" s="3" t="s">
+      <c r="L256" s="3" t="s">
         <v>1286</v>
       </c>
-      <c r="L256" s="3" t="s">
+      <c r="M256" s="3" t="s">
         <v>1287</v>
-      </c>
-      <c r="M256" s="3" t="s">
-        <v>1288</v>
       </c>
       <c r="N256" s="4">
         <v>45666</v>
@@ -24681,19 +24680,19 @@
         <v>45981</v>
       </c>
       <c r="S256" s="3" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="T256" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="U256" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V256" s="3" t="s">
         <v>1289</v>
       </c>
-      <c r="U256" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V256" s="3" t="s">
+      <c r="W256" s="3" t="s">
         <v>1290</v>
-      </c>
-      <c r="W256" s="3" t="s">
-        <v>1291</v>
       </c>
       <c r="X256" s="3" t="s">
         <v>39</v>
@@ -24710,73 +24709,73 @@
     </row>
     <row r="257" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>1292</v>
+        <v>451</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="F257" s="4">
-        <v>45809</v>
+        <v>452</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>1282</v>
+        <v>454</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>1284</v>
+        <v>34</v>
       </c>
       <c r="I257" s="3" t="s">
-        <v>1283</v>
+        <v>34</v>
       </c>
       <c r="J257" s="3" t="s">
-        <v>1285</v>
+        <v>39</v>
       </c>
       <c r="K257" s="3" t="s">
-        <v>1286</v>
+        <v>39</v>
       </c>
       <c r="L257" s="3" t="s">
-        <v>1287</v>
+        <v>34</v>
       </c>
       <c r="M257" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="N257" s="4">
-        <v>45666</v>
-      </c>
-      <c r="O257" s="4">
-        <v>46030</v>
-      </c>
-      <c r="P257" s="4">
-        <v>46065</v>
-      </c>
-      <c r="Q257" s="4">
-        <v>45858</v>
-      </c>
-      <c r="R257" s="4">
-        <v>45981</v>
+        <v>34</v>
+      </c>
+      <c r="N257" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="O257" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="P257" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q257" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="R257" s="3" t="s">
+        <v>459</v>
       </c>
       <c r="S257" s="3" t="s">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="T257" s="3" t="s">
-        <v>1289</v>
+        <v>39</v>
       </c>
       <c r="U257" s="3" t="s">
         <v>39</v>
       </c>
       <c r="V257" s="3" t="s">
-        <v>1290</v>
+        <v>39</v>
       </c>
       <c r="W257" s="3" t="s">
-        <v>1291</v>
+        <v>83</v>
       </c>
       <c r="X257" s="3" t="s">
         <v>39</v>
@@ -24787,133 +24786,123 @@
       <c r="Z257" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AA257" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="AA257" s="3"/>
     </row>
     <row r="258" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>451</v>
+        <v>1292</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>80</v>
+        <v>1293</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>453</v>
+        <v>31</v>
+      </c>
+      <c r="F258" s="4">
+        <v>46072</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>454</v>
+        <v>1294</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I258" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J258" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="K258" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="L258" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M258" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="N258" s="4">
+        <v>45974</v>
+      </c>
+      <c r="O258" s="3"/>
+      <c r="P258" s="3"/>
+      <c r="Q258" s="3"/>
+      <c r="R258" s="3"/>
+      <c r="S258" s="3"/>
+      <c r="T258" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="U258" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J258" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K258" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L258" s="3" t="s">
+      <c r="V258" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W258" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="X258" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M258" s="3" t="s">
+      <c r="Y258" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N258" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="O258" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="P258" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q258" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="R258" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="S258" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="T258" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="U258" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V258" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W258" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="X258" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y258" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="Z258" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AA258" s="3"/>
+      <c r="AA258" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="259" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>1293</v>
+        <v>1302</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>1294</v>
+        <v>87</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F259" s="4">
-        <v>46072</v>
+        <v>46126</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="H259" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I259" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I259" s="3" t="s">
-        <v>1296</v>
-      </c>
       <c r="J259" s="3" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="K259" s="3" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="L259" s="3" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="M259" s="3" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="N259" s="4">
-        <v>45974</v>
+        <v>45957</v>
       </c>
       <c r="O259" s="3"/>
       <c r="P259" s="3"/>
@@ -24921,7 +24910,7 @@
       <c r="R259" s="3"/>
       <c r="S259" s="3"/>
       <c r="T259" s="3" t="s">
-        <v>1301</v>
+        <v>105</v>
       </c>
       <c r="U259" s="3" t="s">
         <v>34</v>
@@ -24930,91 +24919,18 @@
         <v>39</v>
       </c>
       <c r="W259" s="3" t="s">
-        <v>1302</v>
+        <v>1309</v>
       </c>
       <c r="X259" s="3" t="s">
-        <v>34</v>
+        <v>1310</v>
       </c>
       <c r="Y259" s="3" t="s">
-        <v>34</v>
+        <v>1311</v>
       </c>
       <c r="Z259" s="3" t="s">
         <v>39</v>
       </c>
       <c r="AA259" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A260" s="3" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E260" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F260" s="4">
-        <v>46126</v>
-      </c>
-      <c r="G260" s="3" t="s">
-        <v>1304</v>
-      </c>
-      <c r="H260" s="3" t="s">
-        <v>1305</v>
-      </c>
-      <c r="I260" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J260" s="3" t="s">
-        <v>1306</v>
-      </c>
-      <c r="K260" s="3" t="s">
-        <v>1307</v>
-      </c>
-      <c r="L260" s="3" t="s">
-        <v>1308</v>
-      </c>
-      <c r="M260" s="3" t="s">
-        <v>1309</v>
-      </c>
-      <c r="N260" s="4">
-        <v>45957</v>
-      </c>
-      <c r="O260" s="3"/>
-      <c r="P260" s="3"/>
-      <c r="Q260" s="3"/>
-      <c r="R260" s="3"/>
-      <c r="S260" s="3"/>
-      <c r="T260" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="U260" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="V260" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W260" s="3" t="s">
-        <v>1310</v>
-      </c>
-      <c r="X260" s="3" t="s">
-        <v>1311</v>
-      </c>
-      <c r="Y260" s="3" t="s">
-        <v>1312</v>
-      </c>
-      <c r="Z260" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA260" s="3" t="s">
         <v>39</v>
       </c>
     </row>
@@ -25026,7 +24942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R260"/>
+  <dimension ref="A1:R259"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="18" width="44" customWidth="1"/>
@@ -25346,11 +25262,11 @@
       <c r="K6" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L6" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6" t="b">
-        <v>0</v>
+      <c r="L6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N6" s="5" t="b">
         <v>1</v>
@@ -25370,7 +25286,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="5" t="b">
         <v>1</v>
@@ -25402,11 +25318,11 @@
       <c r="K7" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L7" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6" t="b">
-        <v>0</v>
+      <c r="L7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N7" s="5" t="b">
         <v>1</v>
@@ -25426,7 +25342,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="5" t="b">
         <v>1</v>
@@ -25482,7 +25398,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" s="5" t="b">
         <v>1</v>
@@ -25538,7 +25454,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" s="5" t="b">
         <v>1</v>
@@ -25594,7 +25510,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="5" t="b">
         <v>1</v>
@@ -25650,7 +25566,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B12" s="5" t="b">
         <v>1</v>
@@ -25706,7 +25622,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="5" t="b">
         <v>1</v>
@@ -25762,7 +25678,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" s="5" t="b">
         <v>1</v>
@@ -25818,7 +25734,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" s="5" t="b">
         <v>1</v>
@@ -29493,8 +29409,8 @@
       <c r="L80" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="M80" s="6" t="b">
-        <v>0</v>
+      <c r="M80" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N80" s="6" t="b">
         <v>0</v>
@@ -38456,8 +38372,8 @@
       <c r="M240" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="N240" s="5" t="b">
-        <v>1</v>
+      <c r="N240" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="O240" s="6" t="b">
         <v>0</v>
@@ -38474,7 +38390,7 @@
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="B241" s="5" t="b">
         <v>1</v>
@@ -38530,7 +38446,7 @@
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B242" s="5" t="b">
         <v>1</v>
@@ -38586,7 +38502,7 @@
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="B243" s="5" t="b">
         <v>1</v>
@@ -38618,14 +38534,14 @@
       <c r="K243" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L243" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M243" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N243" s="6" t="b">
-        <v>0</v>
+      <c r="L243" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M243" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N243" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="O243" s="6" t="b">
         <v>0</v>
@@ -38642,7 +38558,7 @@
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="B244" s="5" t="b">
         <v>1</v>
@@ -38674,14 +38590,14 @@
       <c r="K244" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L244" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M244" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N244" s="5" t="b">
-        <v>1</v>
+      <c r="L244" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M244" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N244" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="O244" s="6" t="b">
         <v>0</v>
@@ -38698,7 +38614,7 @@
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B245" s="5" t="b">
         <v>1</v>
@@ -38754,7 +38670,7 @@
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B246" s="5" t="b">
         <v>1</v>
@@ -38810,7 +38726,7 @@
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="B247" s="5" t="b">
         <v>1</v>
@@ -38842,17 +38758,17 @@
       <c r="K247" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L247" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M247" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N247" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O247" s="6" t="b">
-        <v>0</v>
+      <c r="L247" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M247" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N247" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O247" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="P247" s="6" t="b">
         <v>0</v>
@@ -38866,7 +38782,7 @@
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>1225</v>
+        <v>1234</v>
       </c>
       <c r="B248" s="5" t="b">
         <v>1</v>
@@ -38907,11 +38823,11 @@
       <c r="N248" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="O248" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P248" s="6" t="b">
-        <v>0</v>
+      <c r="O248" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P248" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="Q248" s="5" t="b">
         <v>1</v>
@@ -38922,7 +38838,7 @@
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B249" s="5" t="b">
         <v>1</v>
@@ -38954,20 +38870,20 @@
       <c r="K249" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L249" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M249" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N249" s="5" t="b">
-        <v>1</v>
+      <c r="L249" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M249" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N249" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="O249" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="P249" s="5" t="b">
-        <v>1</v>
+      <c r="P249" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="Q249" s="5" t="b">
         <v>1</v>
@@ -38978,7 +38894,7 @@
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B250" s="5" t="b">
         <v>1</v>
@@ -39066,20 +38982,20 @@
       <c r="K251" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L251" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M251" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N251" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O251" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P251" s="6" t="b">
-        <v>0</v>
+      <c r="L251" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M251" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N251" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O251" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P251" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="Q251" s="5" t="b">
         <v>1</v>
@@ -39090,7 +39006,7 @@
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="B252" s="5" t="b">
         <v>1</v>
@@ -39146,7 +39062,7 @@
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B253" s="5" t="b">
         <v>1</v>
@@ -39163,8 +39079,8 @@
       <c r="F253" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G253" s="5" t="b">
-        <v>1</v>
+      <c r="G253" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="H253" s="5" t="b">
         <v>1</v>
@@ -39190,8 +39106,8 @@
       <c r="O253" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="P253" s="5" t="b">
-        <v>1</v>
+      <c r="P253" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="Q253" s="5" t="b">
         <v>1</v>
@@ -39202,7 +39118,7 @@
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>1261</v>
+        <v>1270</v>
       </c>
       <c r="B254" s="5" t="b">
         <v>1</v>
@@ -39246,8 +39162,8 @@
       <c r="O254" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="P254" s="6" t="b">
-        <v>0</v>
+      <c r="P254" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="Q254" s="5" t="b">
         <v>1</v>
@@ -39258,7 +39174,7 @@
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="B255" s="5" t="b">
         <v>1</v>
@@ -39275,8 +39191,8 @@
       <c r="F255" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="G255" s="6" t="b">
-        <v>0</v>
+      <c r="G255" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="H255" s="5" t="b">
         <v>1</v>
@@ -39302,8 +39218,8 @@
       <c r="O255" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="P255" s="5" t="b">
-        <v>1</v>
+      <c r="P255" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="Q255" s="5" t="b">
         <v>1</v>
@@ -39314,7 +39230,7 @@
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>1280</v>
+        <v>1291</v>
       </c>
       <c r="B256" s="5" t="b">
         <v>1</v>
@@ -39370,7 +39286,7 @@
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>1292</v>
+        <v>451</v>
       </c>
       <c r="B257" s="5" t="b">
         <v>1</v>
@@ -39378,26 +39294,26 @@
       <c r="C257" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="D257" s="5" t="b">
-        <v>1</v>
+      <c r="D257" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="E257" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F257" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G257" s="5" t="b">
-        <v>1</v>
+      <c r="F257" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G257" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="H257" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="I257" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J257" s="5" t="b">
-        <v>1</v>
+      <c r="I257" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J257" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="K257" s="5" t="b">
         <v>1</v>
@@ -39414,19 +39330,19 @@
       <c r="O257" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="P257" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q257" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R257" s="5" t="b">
-        <v>1</v>
+      <c r="P257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q257" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R257" s="6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>451</v>
+        <v>1292</v>
       </c>
       <c r="B258" s="5" t="b">
         <v>1</v>
@@ -39434,8 +39350,8 @@
       <c r="C258" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="D258" s="6" t="b">
-        <v>0</v>
+      <c r="D258" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="E258" s="5" t="b">
         <v>1</v>
@@ -39443,46 +39359,46 @@
       <c r="F258" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G258" s="6" t="b">
-        <v>0</v>
+      <c r="G258" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="H258" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="I258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J258" s="6" t="b">
-        <v>0</v>
+      <c r="I258" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J258" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="K258" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L258" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M258" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N258" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O258" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P258" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q258" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R258" s="6" t="b">
-        <v>0</v>
+      <c r="L258" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M258" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N258" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O258" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P258" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q258" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R258" s="5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>1293</v>
+        <v>1302</v>
       </c>
       <c r="B259" s="5" t="b">
         <v>1</v>
@@ -39496,11 +39412,11 @@
       <c r="E259" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F259" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G259" s="5" t="b">
-        <v>1</v>
+      <c r="F259" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G259" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="H259" s="5" t="b">
         <v>1</v>
@@ -39533,62 +39449,6 @@
         <v>1</v>
       </c>
       <c r="R259" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A260" s="3" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="C260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G260" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L260" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M260" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N260" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O260" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P260" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R260" s="5" t="b">
         <v>1</v>
       </c>
     </row>

--- a/report/merged_configurations.xlsx
+++ b/report/merged_configurations.xlsx
@@ -3938,7 +3938,7 @@
     <t>[{"name":"Verslag Business Werkgroep - 5 maart 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/reports/Verslag%20Nuding%20Down%20Night%20Noise%20business%20werkgroep%2005-03-2026%20(1).pdf"},{"name":"Verslag Thematische Werkgroep 1 - 2 april 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/reports/Verslag%20TW1%20OSLO%20NDNN%2014-04%20.pdf"},{"name":"Verslag Thematische Werkgroep 2 - 6 mei 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/reports/Verslag%20TW2%20OSLO%20NDNN%2006.05.2026%20.pdf"}]</t>
   </si>
   <si>
-    <t>[{"name":"Presentatie Business Werkgroep -  5 maart 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/presentations/Presentatie%20Business%20Werkgroep%20NDNN%2005-03-2026.pdf"},{"name":"Presentatie Thematische Werkgroep - 2 april 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/presentations/Presentatie%20Thematische%20werkgroep%201%20NDNN%2002-04-2026.pdf"},{"name":"Presentatie Thematische Werkgroep 2 - 5 mei 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/presentations/Presentatie%20NDNN%20Thematische%20werkgroep%202.pdf"}]</t>
+    <t>[{"name":"Presentatie Business Werkgroep -  5 maart 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/presentations/Presentatie%20Business%20Werkgroep%20NDNN%2005-03-2026.pdf"},{"name":"Presentatie Thematische Werkgroep - 2 april 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/presentations/Presentatie%20Thematische%20werkgroep%201%20NDNN%2002-04-2026.pdf"},{"name":"Presentatie Thematische Werkgroep 2 - 5 mei 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/presentations/Presentatie%20NDNN%20Thematische%20werkgroep%202.pdf"},{"name":"Presentatie Thematische Werkgroep 3 - 12 juni 2026","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/presentations/Presentatie%20NDNN%20Thematische%20werkgroep%203.pdf"}]</t>
   </si>
   <si>
     <t>{"name":"Charter NDNN","resourceReference":"https://raw.githubusercontent.com/Informatievlaanderen/OSLOthema-NDNN/standaardenregister/charter/Werkgroep%20charter%20OSLO_NudgingDownNightNoise.pdf"}</t>
